--- a/youzi/老中医/index.xlsx
+++ b/youzi/老中医/index.xlsx
@@ -39,55 +39,2011 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD93343"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC22937"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BE77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DCB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA849"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D9DC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE56A76"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7DC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4756"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEB8F98"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1E8136"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,97 +2055,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1F8638"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,349 +2073,1357 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3C4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BE77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB564"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0AAB1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
+        <fgColor rgb="FFF3BBC1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -555,193 +3435,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -753,7 +3465,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA858F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -765,2755 +3513,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DCB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D9DC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA849"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7DC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4756"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3C4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9689,40 +9689,40 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="8">
         <v>3.21</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="9">
         <v>13.58</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="2">
         <v>10.09</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="10">
         <v>10.64</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="4">
         <v>5.23</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="11">
         <v>7.71</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="6">
         <v>7.43</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="12">
         <v>10.09</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="5">
         <v>3.67</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="3">
         <v>2.75</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="7">
         <v>-1.38</v>
       </c>
-      <c r="T2" s="10">
+      <c r="T2" s="1">
         <v>-38.17</v>
       </c>
     </row>
@@ -9751,40 +9751,40 @@
       <c r="H3">
         <v>1.53</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="18">
         <v>8.3</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="19">
         <v>12.74</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="22">
         <v>3.87</v>
       </c>
       <c r="L3" s="23">
         <v>6.42</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="15">
         <v>11.13</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="16">
         <v>22.26</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="24">
         <v>23.58</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="20">
         <v>28.87</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="17">
         <v>33.3</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="21">
         <v>27.64</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="13">
         <v>20.09</v>
       </c>
-      <c r="T3" s="18">
+      <c r="T3" s="14">
         <v>-21.32</v>
       </c>
     </row>
@@ -9813,37 +9813,37 @@
       <c r="H4">
         <v>-3.75</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="33">
         <v>8.14</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="28">
         <v>-0.36</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="29">
         <v>2.08</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="25">
         <v>6.61</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="30">
         <v>17.29</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="34">
         <v>18.55</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="35">
         <v>23.62</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="26">
         <v>27.87</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="36">
         <v>22.44</v>
       </c>
-      <c r="R4" s="25">
+      <c r="R4" s="32">
         <v>15.2</v>
       </c>
-      <c r="S4" s="26">
+      <c r="S4" s="31">
         <v>12.58</v>
       </c>
       <c r="T4" s="27">
@@ -9875,28 +9875,28 @@
       <c r="H5">
         <v>-0.83</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="45">
         <v>-5.04</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="46">
         <v>-5.88</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="47">
         <v>-9.66</v>
       </c>
-      <c r="L5" s="37">
+      <c r="L5" s="39">
         <v>-8.82</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="40">
         <v>-12.02</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="37">
         <v>-12.61</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="41">
         <v>-16.22</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="48">
         <v>-15.13</v>
       </c>
       <c r="Q5" s="42">
@@ -9905,10 +9905,10 @@
       <c r="R5" s="43">
         <v>-16.22</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="38">
         <v>-15.13</v>
       </c>
-      <c r="T5" s="39">
+      <c r="T5" s="44">
         <v>-43.36</v>
       </c>
     </row>
@@ -9937,40 +9937,40 @@
       <c r="H6">
         <v>-0.24</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="58">
         <v>-2.16</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="55">
         <v>-2.4</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="56">
         <v>-5.05</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="49">
         <v>-3.37</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="50">
         <v>-4.81</v>
       </c>
-      <c r="N6" s="50">
+      <c r="N6" s="51">
         <v>-1.2</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="59">
         <v>-3.85</v>
       </c>
-      <c r="P6" s="51">
+      <c r="P6" s="57">
         <v>-2.64</v>
       </c>
       <c r="Q6" s="52">
         <v>0.48</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="53">
         <v>0.24</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="60">
         <v>-0.24</v>
       </c>
-      <c r="T6" s="58">
+      <c r="T6" s="54">
         <v>33.41</v>
       </c>
     </row>
@@ -9999,34 +9999,34 @@
       <c r="H7">
         <v>-1.58</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="68">
         <v>7.2</v>
       </c>
       <c r="J7" s="63">
         <v>9.53</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="64">
         <v>10.1</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="69">
         <v>11.2</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="65">
         <v>15.78</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="66">
         <v>11.36</v>
       </c>
-      <c r="O7" s="61">
+      <c r="O7" s="70">
         <v>11.51</v>
       </c>
-      <c r="P7" s="65">
+      <c r="P7" s="71">
         <v>22.68</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="72">
         <v>13.03</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="61">
         <v>13.07</v>
       </c>
       <c r="S7" s="67">
@@ -10061,40 +10061,40 @@
       <c r="H8">
         <v>-2.93</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="81">
         <v>1.94</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="80">
         <v>4.62</v>
       </c>
-      <c r="K8" s="75">
+      <c r="K8" s="82">
         <v>-0.95</v>
       </c>
-      <c r="L8" s="73">
+      <c r="L8" s="83">
         <v>0.22</v>
       </c>
-      <c r="M8" s="76">
+      <c r="M8" s="84">
         <v>7.42</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="73">
         <v>13.89</v>
       </c>
-      <c r="O8" s="77">
+      <c r="O8" s="76">
         <v>15.44</v>
       </c>
-      <c r="P8" s="78">
+      <c r="P8" s="74">
         <v>27.01</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="77">
         <v>27.22</v>
       </c>
-      <c r="R8" s="74">
+      <c r="R8" s="75">
         <v>15.14</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="78">
         <v>10.7</v>
       </c>
-      <c r="T8" s="83">
+      <c r="T8" s="79">
         <v>-23.94</v>
       </c>
     </row>
@@ -10123,40 +10123,40 @@
       <c r="H9">
         <v>-1.7</v>
       </c>
-      <c r="I9" s="88">
+      <c r="I9" s="93">
         <v>0.24</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="94">
         <v>1.92</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="85">
         <v>-2.26</v>
       </c>
-      <c r="L9" s="89">
+      <c r="L9" s="96">
         <v>-1.76</v>
       </c>
-      <c r="M9" s="87">
+      <c r="M9" s="90">
         <v>-1.81</v>
       </c>
-      <c r="N9" s="90">
+      <c r="N9" s="95">
         <v>-0.43</v>
       </c>
-      <c r="O9" s="85">
+      <c r="O9" s="86">
         <v>6.75</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="87">
         <v>9.69</v>
       </c>
-      <c r="Q9" s="86">
+      <c r="Q9" s="91">
         <v>8.65</v>
       </c>
-      <c r="R9" s="91">
+      <c r="R9" s="88">
         <v>12.49</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="89">
         <v>12.78</v>
       </c>
-      <c r="T9" s="96">
+      <c r="T9" s="92">
         <v>18.98</v>
       </c>
     </row>
@@ -10188,37 +10188,37 @@
       <c r="I10" s="97">
         <v>1.92</v>
       </c>
-      <c r="J10" s="102">
+      <c r="J10" s="104">
         <v>-2.26</v>
       </c>
-      <c r="K10" s="98">
+      <c r="K10" s="106">
         <v>-1.76</v>
       </c>
-      <c r="L10" s="104">
+      <c r="L10" s="99">
         <v>-1.81</v>
       </c>
-      <c r="M10" s="99">
+      <c r="M10" s="100">
         <v>-0.43</v>
       </c>
-      <c r="N10" s="103">
+      <c r="N10" s="107">
         <v>6.75</v>
       </c>
-      <c r="O10" s="100">
+      <c r="O10" s="101">
         <v>9.69</v>
       </c>
-      <c r="P10" s="107">
+      <c r="P10" s="98">
         <v>8.65</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="102">
         <v>12.49</v>
       </c>
-      <c r="R10" s="101">
+      <c r="R10" s="105">
         <v>12.78</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="103">
         <v>19.76</v>
       </c>
-      <c r="T10" s="106">
+      <c r="T10" s="108">
         <v>18.98</v>
       </c>
     </row>
@@ -10247,40 +10247,40 @@
       <c r="H11">
         <v>3.83</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="112">
         <v>5.97</v>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="109">
         <v>5.54</v>
       </c>
-      <c r="K11" s="111">
+      <c r="K11" s="110">
         <v>1.42</v>
       </c>
-      <c r="L11" s="113">
+      <c r="L11" s="114">
         <v>4.12</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="115">
         <v>9.38</v>
       </c>
-      <c r="N11" s="109">
+      <c r="N11" s="111">
         <v>11.65</v>
       </c>
-      <c r="O11" s="115">
+      <c r="O11" s="119">
         <v>9.09</v>
       </c>
-      <c r="P11" s="114">
+      <c r="P11" s="113">
         <v>4.55</v>
       </c>
       <c r="Q11" s="116">
         <v>3.69</v>
       </c>
-      <c r="R11" s="110">
+      <c r="R11" s="117">
         <v>4.12</v>
       </c>
-      <c r="S11" s="112">
+      <c r="S11" s="118">
         <v>3.84</v>
       </c>
-      <c r="T11" s="117">
+      <c r="T11" s="120">
         <v>32.81</v>
       </c>
     </row>
@@ -10309,40 +10309,40 @@
       <c r="H12">
         <v>1.24</v>
       </c>
-      <c r="I12" s="127">
+      <c r="I12" s="131">
         <v>0.19</v>
       </c>
-      <c r="J12" s="129">
+      <c r="J12" s="122">
         <v>10.2</v>
       </c>
-      <c r="K12" s="122">
+      <c r="K12" s="127">
         <v>15.11</v>
       </c>
       <c r="L12" s="123">
         <v>9.35</v>
       </c>
-      <c r="M12" s="130">
+      <c r="M12" s="132">
         <v>12.65</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="129">
         <v>13.31</v>
       </c>
-      <c r="O12" s="132">
+      <c r="O12" s="124">
         <v>15.49</v>
       </c>
-      <c r="P12" s="126">
+      <c r="P12" s="128">
         <v>12.37</v>
       </c>
-      <c r="Q12" s="128">
+      <c r="Q12" s="125">
         <v>12.09</v>
       </c>
-      <c r="R12" s="121">
+      <c r="R12" s="130">
         <v>7.84</v>
       </c>
-      <c r="S12" s="124">
+      <c r="S12" s="126">
         <v>8.97</v>
       </c>
-      <c r="T12" s="125">
+      <c r="T12" s="121">
         <v>-16.15</v>
       </c>
     </row>
@@ -10371,40 +10371,40 @@
       <c r="H13">
         <v>0.12</v>
       </c>
-      <c r="I13" s="133">
+      <c r="I13" s="140">
         <v>9.88</v>
       </c>
-      <c r="J13" s="139">
+      <c r="J13" s="133">
         <v>16.74</v>
       </c>
-      <c r="K13" s="140">
+      <c r="K13" s="141">
         <v>13.25</v>
       </c>
-      <c r="L13" s="141">
+      <c r="L13" s="142">
         <v>7.57</v>
       </c>
-      <c r="M13" s="134">
+      <c r="M13" s="143">
         <v>1.63</v>
       </c>
-      <c r="N13" s="136">
+      <c r="N13" s="144">
         <v>2.04</v>
       </c>
-      <c r="O13" s="143">
+      <c r="O13" s="134">
         <v>3.78</v>
       </c>
-      <c r="P13" s="137">
+      <c r="P13" s="136">
         <v>0.24</v>
       </c>
-      <c r="Q13" s="135">
+      <c r="Q13" s="138">
         <v>-1.39</v>
       </c>
-      <c r="R13" s="138">
+      <c r="R13" s="137">
         <v>-1.48</v>
       </c>
-      <c r="S13" s="142">
+      <c r="S13" s="139">
         <v>-3.64</v>
       </c>
-      <c r="T13" s="144">
+      <c r="T13" s="135">
         <v>-18.98</v>
       </c>
     </row>
@@ -10433,40 +10433,40 @@
       <c r="H14">
         <v>-0.7</v>
       </c>
-      <c r="I14" s="154">
+      <c r="I14" s="149">
         <v>1.82</v>
       </c>
-      <c r="J14" s="146">
+      <c r="J14" s="155">
         <v>-2</v>
       </c>
-      <c r="K14" s="147">
+      <c r="K14" s="156">
         <v>-1.98</v>
       </c>
-      <c r="L14" s="152">
+      <c r="L14" s="145">
         <v>2.53</v>
       </c>
-      <c r="M14" s="155">
+      <c r="M14" s="151">
         <v>10.14</v>
       </c>
-      <c r="N14" s="148">
+      <c r="N14" s="147">
         <v>14.17</v>
       </c>
-      <c r="O14" s="156">
+      <c r="O14" s="146">
         <v>12.5</v>
       </c>
-      <c r="P14" s="149">
+      <c r="P14" s="152">
         <v>17.86</v>
       </c>
-      <c r="Q14" s="150">
+      <c r="Q14" s="153">
         <v>15.7</v>
       </c>
-      <c r="R14" s="145">
+      <c r="R14" s="154">
         <v>13.49</v>
       </c>
-      <c r="S14" s="151">
+      <c r="S14" s="150">
         <v>4.66</v>
       </c>
-      <c r="T14" s="153">
+      <c r="T14" s="148">
         <v>-6.15</v>
       </c>
     </row>
@@ -10495,40 +10495,40 @@
       <c r="H15">
         <v>-0.95</v>
       </c>
-      <c r="I15" s="159">
+      <c r="I15" s="158">
         <v>-0.85</v>
       </c>
-      <c r="J15" s="157">
+      <c r="J15" s="164">
         <v>-10.76</v>
       </c>
       <c r="K15" s="160">
         <v>-14.5</v>
       </c>
-      <c r="L15" s="161">
+      <c r="L15" s="159">
         <v>-17.38</v>
       </c>
-      <c r="M15" s="162">
+      <c r="M15" s="161">
         <v>-11.49</v>
       </c>
-      <c r="N15" s="163">
+      <c r="N15" s="165">
         <v>-16.08</v>
       </c>
-      <c r="O15" s="166">
+      <c r="O15" s="168">
         <v>-7.7</v>
       </c>
-      <c r="P15" s="164">
+      <c r="P15" s="166">
         <v>1.53</v>
       </c>
-      <c r="Q15" s="168">
+      <c r="Q15" s="162">
         <v>11.66</v>
       </c>
-      <c r="R15" s="158">
+      <c r="R15" s="167">
         <v>22.82</v>
       </c>
-      <c r="S15" s="165">
+      <c r="S15" s="163">
         <v>17.95</v>
       </c>
-      <c r="T15" s="167">
+      <c r="T15" s="157">
         <v>94.79</v>
       </c>
     </row>
@@ -10557,40 +10557,40 @@
       <c r="H16">
         <v>0.86</v>
       </c>
-      <c r="I16" s="169">
+      <c r="I16" s="173">
         <v>5.26</v>
       </c>
-      <c r="J16" s="179">
+      <c r="J16" s="177">
         <v>6.4</v>
       </c>
-      <c r="K16" s="174">
+      <c r="K16" s="171">
         <v>12.52</v>
       </c>
-      <c r="L16" s="172">
+      <c r="L16" s="178">
         <v>2.7</v>
       </c>
-      <c r="M16" s="170">
+      <c r="M16" s="179">
         <v>-7.54</v>
       </c>
       <c r="N16" s="175">
         <v>-14.94</v>
       </c>
-      <c r="O16" s="171">
+      <c r="O16" s="180">
         <v>-13.09</v>
       </c>
-      <c r="P16" s="176">
+      <c r="P16" s="174">
         <v>-15.93</v>
       </c>
-      <c r="Q16" s="173">
+      <c r="Q16" s="169">
         <v>-17.35</v>
       </c>
-      <c r="R16" s="177">
+      <c r="R16" s="170">
         <v>-9.1</v>
       </c>
-      <c r="S16" s="178">
+      <c r="S16" s="176">
         <v>-8.25</v>
       </c>
-      <c r="T16" s="180">
+      <c r="T16" s="172">
         <v>-37.41</v>
       </c>
     </row>
@@ -10628,31 +10628,31 @@
       <c r="K17" s="186">
         <v>5.3</v>
       </c>
-      <c r="L17" s="187">
+      <c r="L17" s="190">
         <v>-3.58</v>
       </c>
-      <c r="M17" s="182">
+      <c r="M17" s="183">
         <v>-8.37</v>
       </c>
-      <c r="N17" s="188">
+      <c r="N17" s="184">
         <v>-13.99</v>
       </c>
-      <c r="O17" s="189">
+      <c r="O17" s="191">
         <v>-9.72</v>
       </c>
-      <c r="P17" s="183">
+      <c r="P17" s="187">
         <v>-9.62</v>
       </c>
-      <c r="Q17" s="184">
+      <c r="Q17" s="185">
         <v>-13.01</v>
       </c>
-      <c r="R17" s="190">
+      <c r="R17" s="188">
         <v>-9.84</v>
       </c>
-      <c r="S17" s="191">
+      <c r="S17" s="182">
         <v>-7.26</v>
       </c>
-      <c r="T17" s="185">
+      <c r="T17" s="189">
         <v>-22.11</v>
       </c>
     </row>
@@ -10681,40 +10681,40 @@
       <c r="H18">
         <v>1.07</v>
       </c>
-      <c r="I18" s="204">
+      <c r="I18" s="199">
         <v>6.93</v>
       </c>
-      <c r="J18" s="201">
+      <c r="J18" s="200">
         <v>11.13</v>
       </c>
-      <c r="K18" s="193">
+      <c r="K18" s="195">
         <v>13.33</v>
       </c>
-      <c r="L18" s="197">
+      <c r="L18" s="204">
         <v>4.5</v>
       </c>
-      <c r="M18" s="202">
+      <c r="M18" s="196">
         <v>-0.96</v>
       </c>
-      <c r="N18" s="203">
+      <c r="N18" s="197">
         <v>-7.85</v>
       </c>
-      <c r="O18" s="194">
+      <c r="O18" s="201">
         <v>1.38</v>
       </c>
       <c r="P18" s="198">
         <v>-1.51</v>
       </c>
-      <c r="Q18" s="199">
+      <c r="Q18" s="202">
         <v>-0.6</v>
       </c>
-      <c r="R18" s="200">
+      <c r="R18" s="193">
         <v>5.78</v>
       </c>
-      <c r="S18" s="195">
+      <c r="S18" s="194">
         <v>7.69</v>
       </c>
-      <c r="T18" s="196">
+      <c r="T18" s="203">
         <v>5.35</v>
       </c>
     </row>
@@ -10743,40 +10743,40 @@
       <c r="H19">
         <v>-3.11</v>
       </c>
-      <c r="I19" s="205">
+      <c r="I19" s="213">
         <v>13.55</v>
       </c>
-      <c r="J19" s="208">
+      <c r="J19" s="206">
         <v>24.91</v>
       </c>
-      <c r="K19" s="211">
+      <c r="K19" s="216">
         <v>37.43</v>
       </c>
-      <c r="L19" s="212">
+      <c r="L19" s="214">
         <v>23.65</v>
       </c>
-      <c r="M19" s="209">
+      <c r="M19" s="210">
         <v>11.25</v>
       </c>
-      <c r="N19" s="206">
+      <c r="N19" s="207">
         <v>14.01</v>
       </c>
-      <c r="O19" s="213">
+      <c r="O19" s="208">
         <v>7.23</v>
       </c>
-      <c r="P19" s="214">
+      <c r="P19" s="211">
         <v>11.94</v>
       </c>
-      <c r="Q19" s="215">
+      <c r="Q19" s="212">
         <v>23.19</v>
       </c>
-      <c r="R19" s="210">
+      <c r="R19" s="215">
         <v>30.54</v>
       </c>
-      <c r="S19" s="207">
+      <c r="S19" s="209">
         <v>43.63</v>
       </c>
-      <c r="T19" s="216">
+      <c r="T19" s="205">
         <v>23.65</v>
       </c>
     </row>
@@ -10806,40 +10806,40 @@
       <c r="H20">
         <v>0.33</v>
       </c>
-      <c r="I20" s="228">
+      <c r="I20" s="218">
         <v>-4.25</v>
       </c>
-      <c r="J20" s="226">
+      <c r="J20" s="224">
         <v>-3.47</v>
       </c>
-      <c r="K20" s="223">
+      <c r="K20" s="219">
         <v>-11.03</v>
       </c>
-      <c r="L20" s="218">
+      <c r="L20" s="226">
         <v>-2.14</v>
       </c>
-      <c r="M20" s="219">
+      <c r="M20" s="227">
         <v>1.36</v>
       </c>
       <c r="N20" s="220">
         <v>0.92</v>
       </c>
-      <c r="O20" s="224">
+      <c r="O20" s="228">
         <v>-0.69</v>
       </c>
-      <c r="P20" s="221">
+      <c r="P20" s="222">
         <v>-0.81</v>
       </c>
-      <c r="Q20" s="222">
+      <c r="Q20" s="217">
         <v>-4.89</v>
       </c>
-      <c r="R20" s="227">
+      <c r="R20" s="221">
         <v>-7.48</v>
       </c>
-      <c r="S20" s="225">
+      <c r="S20" s="223">
         <v>-11.67</v>
       </c>
-      <c r="T20" s="217">
+      <c r="T20" s="225">
         <v>3.67</v>
       </c>
     </row>
@@ -10869,7 +10869,7 @@
       <c r="H21">
         <v>3.45</v>
       </c>
-      <c r="I21" s="232">
+      <c r="I21" s="229">
         <v>-1.4</v>
       </c>
       <c r="J21" s="237">
@@ -10878,31 +10878,31 @@
       <c r="K21" s="230">
         <v>-8.85</v>
       </c>
-      <c r="L21" s="234">
+      <c r="L21" s="235">
         <v>0.26</v>
       </c>
       <c r="M21" s="238">
         <v>7.8</v>
       </c>
-      <c r="N21" s="235">
+      <c r="N21" s="231">
         <v>18.58</v>
       </c>
-      <c r="O21" s="233">
+      <c r="O21" s="239">
         <v>6.75</v>
       </c>
       <c r="P21" s="236">
         <v>6.05</v>
       </c>
-      <c r="Q21" s="239">
+      <c r="Q21" s="232">
         <v>5.08</v>
       </c>
-      <c r="R21" s="240">
+      <c r="R21" s="233">
         <v>0.53</v>
       </c>
-      <c r="S21" s="231">
+      <c r="S21" s="234">
         <v>-3.42</v>
       </c>
-      <c r="T21" s="229">
+      <c r="T21" s="240">
         <v>-15.95</v>
       </c>
     </row>
@@ -10935,37 +10935,37 @@
       <c r="I22" s="252">
         <v>-1.57</v>
       </c>
-      <c r="J22" s="249">
+      <c r="J22" s="248">
         <v>-11.43</v>
       </c>
-      <c r="K22" s="250">
+      <c r="K22" s="247">
         <v>-20.29</v>
       </c>
       <c r="L22" s="241">
         <v>-20.43</v>
       </c>
-      <c r="M22" s="251">
+      <c r="M22" s="242">
         <v>-23.79</v>
       </c>
-      <c r="N22" s="246">
+      <c r="N22" s="249">
         <v>-23.86</v>
       </c>
-      <c r="O22" s="245">
+      <c r="O22" s="243">
         <v>-20.14</v>
       </c>
-      <c r="P22" s="242">
+      <c r="P22" s="244">
         <v>-20.57</v>
       </c>
-      <c r="Q22" s="243">
+      <c r="Q22" s="245">
         <v>-19.71</v>
       </c>
-      <c r="R22" s="244">
+      <c r="R22" s="250">
         <v>-17.86</v>
       </c>
-      <c r="S22" s="247">
+      <c r="S22" s="251">
         <v>-13.57</v>
       </c>
-      <c r="T22" s="248">
+      <c r="T22" s="246">
         <v>-9.93</v>
       </c>
     </row>
@@ -10994,40 +10994,40 @@
       <c r="H23">
         <v>-1.94</v>
       </c>
-      <c r="I23" s="253">
+      <c r="I23" s="257">
         <v>-0.19</v>
       </c>
-      <c r="J23" s="257">
+      <c r="J23" s="261">
         <v>2.17</v>
       </c>
-      <c r="K23" s="254">
+      <c r="K23" s="258">
         <v>0.75</v>
       </c>
-      <c r="L23" s="260">
+      <c r="L23" s="262">
         <v>-3.02</v>
       </c>
-      <c r="M23" s="255">
+      <c r="M23" s="263">
         <v>-8.11</v>
       </c>
-      <c r="N23" s="261">
+      <c r="N23" s="264">
         <v>-10.74</v>
       </c>
-      <c r="O23" s="258">
+      <c r="O23" s="259">
         <v>-13.2</v>
       </c>
-      <c r="P23" s="262">
+      <c r="P23" s="253">
         <v>-12.72</v>
       </c>
-      <c r="Q23" s="256">
+      <c r="Q23" s="254">
         <v>-15.55</v>
       </c>
-      <c r="R23" s="263">
+      <c r="R23" s="256">
         <v>-14.99</v>
       </c>
-      <c r="S23" s="264">
+      <c r="S23" s="255">
         <v>-14.61</v>
       </c>
-      <c r="T23" s="259">
+      <c r="T23" s="260">
         <v>-23.09</v>
       </c>
     </row>
@@ -11056,40 +11056,40 @@
       <c r="H24">
         <v>5.07</v>
       </c>
-      <c r="I24" s="269">
+      <c r="I24" s="271">
         <v>4.74</v>
       </c>
-      <c r="J24" s="270">
+      <c r="J24" s="273">
         <v>8.49</v>
       </c>
-      <c r="K24" s="276">
+      <c r="K24" s="274">
         <v>19.3</v>
       </c>
-      <c r="L24" s="271">
+      <c r="L24" s="265">
         <v>7.42</v>
       </c>
-      <c r="M24" s="265">
+      <c r="M24" s="275">
         <v>-3.31</v>
       </c>
-      <c r="N24" s="266">
+      <c r="N24" s="276">
         <v>-12.15</v>
       </c>
-      <c r="O24" s="267">
+      <c r="O24" s="266">
         <v>-3.4</v>
       </c>
-      <c r="P24" s="273">
+      <c r="P24" s="267">
         <v>-10.01</v>
       </c>
-      <c r="Q24" s="274">
+      <c r="Q24" s="270">
         <v>-19.03</v>
       </c>
-      <c r="R24" s="272">
+      <c r="R24" s="268">
         <v>-27.17</v>
       </c>
-      <c r="S24" s="275">
+      <c r="S24" s="269">
         <v>-25.92</v>
       </c>
-      <c r="T24" s="268">
+      <c r="T24" s="272">
         <v>-26.99</v>
       </c>
     </row>
@@ -11118,22 +11118,22 @@
       <c r="H25">
         <v>-1.3</v>
       </c>
-      <c r="I25" s="283">
+      <c r="I25" s="284">
         <v>4.38</v>
       </c>
-      <c r="J25" s="280">
+      <c r="J25" s="285">
         <v>12.4</v>
       </c>
-      <c r="K25" s="287">
+      <c r="K25" s="282">
         <v>12.8</v>
       </c>
-      <c r="L25" s="285">
+      <c r="L25" s="288">
         <v>15.71</v>
       </c>
-      <c r="M25" s="288">
+      <c r="M25" s="283">
         <v>22.51</v>
       </c>
-      <c r="N25" s="281">
+      <c r="N25" s="286">
         <v>10.26</v>
       </c>
       <c r="O25" s="277">
@@ -11142,16 +11142,16 @@
       <c r="P25" s="278">
         <v>-7.99</v>
       </c>
-      <c r="Q25" s="286">
+      <c r="Q25" s="287">
         <v>-6.89</v>
       </c>
       <c r="R25" s="279">
         <v>-11.49</v>
       </c>
-      <c r="S25" s="284">
+      <c r="S25" s="280">
         <v>-17.58</v>
       </c>
-      <c r="T25" s="282">
+      <c r="T25" s="281">
         <v>-22.39</v>
       </c>
     </row>
@@ -11181,40 +11181,40 @@
       <c r="H26">
         <v>-2.57</v>
       </c>
-      <c r="I26" s="292">
+      <c r="I26" s="289">
         <v>10.44</v>
       </c>
-      <c r="J26" s="289">
+      <c r="J26" s="297">
         <v>3.45</v>
       </c>
-      <c r="K26" s="295">
+      <c r="K26" s="290">
         <v>5.27</v>
       </c>
-      <c r="L26" s="293">
+      <c r="L26" s="294">
         <v>9.45</v>
       </c>
-      <c r="M26" s="294">
+      <c r="M26" s="292">
         <v>20.4</v>
       </c>
-      <c r="N26" s="290">
+      <c r="N26" s="295">
         <v>25.42</v>
       </c>
-      <c r="O26" s="297">
+      <c r="O26" s="291">
         <v>22.51</v>
       </c>
-      <c r="P26" s="291">
+      <c r="P26" s="298">
         <v>10.26</v>
       </c>
-      <c r="Q26" s="296">
+      <c r="Q26" s="299">
         <v>5.17</v>
       </c>
-      <c r="R26" s="298">
+      <c r="R26" s="300">
         <v>8.26</v>
       </c>
-      <c r="S26" s="299">
+      <c r="S26" s="296">
         <v>1.19</v>
       </c>
-      <c r="T26" s="300">
+      <c r="T26" s="293">
         <v>2.69</v>
       </c>
     </row>
@@ -11243,40 +11243,40 @@
       <c r="H27">
         <v>-1.11</v>
       </c>
-      <c r="I27" s="311">
+      <c r="I27" s="301">
         <v>11.23</v>
       </c>
-      <c r="J27" s="312">
+      <c r="J27" s="308">
         <v>9.47</v>
       </c>
-      <c r="K27" s="308">
+      <c r="K27" s="309">
         <v>17.89</v>
       </c>
-      <c r="L27" s="305">
+      <c r="L27" s="310">
         <v>15.65</v>
       </c>
-      <c r="M27" s="301">
+      <c r="M27" s="304">
         <v>27.16</v>
       </c>
-      <c r="N27" s="306">
+      <c r="N27" s="311">
         <v>14.46</v>
       </c>
-      <c r="O27" s="309">
+      <c r="O27" s="312">
         <v>3.02</v>
       </c>
       <c r="P27" s="307">
         <v>-7.3</v>
       </c>
-      <c r="Q27" s="302">
+      <c r="Q27" s="305">
         <v>-16.56</v>
       </c>
-      <c r="R27" s="303">
+      <c r="R27" s="302">
         <v>-21.68</v>
       </c>
-      <c r="S27" s="304">
+      <c r="S27" s="306">
         <v>-18.25</v>
       </c>
-      <c r="T27" s="310">
+      <c r="T27" s="303">
         <v>52</v>
       </c>
     </row>
@@ -11305,40 +11305,40 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28" s="319">
+      <c r="I28" s="324">
         <v>7.84</v>
       </c>
-      <c r="J28" s="323">
+      <c r="J28" s="316">
         <v>10.96</v>
       </c>
-      <c r="K28" s="320">
+      <c r="K28" s="313">
         <v>23.57</v>
       </c>
-      <c r="L28" s="316">
+      <c r="L28" s="314">
         <v>27.94</v>
       </c>
-      <c r="M28" s="321">
+      <c r="M28" s="319">
         <v>35.94</v>
       </c>
-      <c r="N28" s="322">
+      <c r="N28" s="315">
         <v>20.4</v>
       </c>
-      <c r="O28" s="317">
+      <c r="O28" s="322">
         <v>17.96</v>
       </c>
-      <c r="P28" s="324">
+      <c r="P28" s="323">
         <v>37.01</v>
       </c>
-      <c r="Q28" s="313">
+      <c r="Q28" s="317">
         <v>21.7</v>
       </c>
-      <c r="R28" s="318">
+      <c r="R28" s="320">
         <v>12.72</v>
       </c>
-      <c r="S28" s="314">
+      <c r="S28" s="318">
         <v>19.21</v>
       </c>
-      <c r="T28" s="315">
+      <c r="T28" s="321">
         <v>4.54</v>
       </c>
     </row>
@@ -11367,40 +11367,40 @@
       <c r="H29">
         <v>-1.84</v>
       </c>
-      <c r="I29" s="328">
+      <c r="I29" s="326">
         <v>3.5</v>
       </c>
-      <c r="J29" s="331">
+      <c r="J29" s="332">
         <v>3.9</v>
       </c>
-      <c r="K29" s="329">
+      <c r="K29" s="327">
         <v>6</v>
       </c>
-      <c r="L29" s="332">
+      <c r="L29" s="328">
         <v>0.91</v>
       </c>
-      <c r="M29" s="333">
+      <c r="M29" s="329">
         <v>2.31</v>
       </c>
-      <c r="N29" s="326">
+      <c r="N29" s="330">
         <v>-2.33</v>
       </c>
-      <c r="O29" s="330">
+      <c r="O29" s="331">
         <v>4.44</v>
       </c>
       <c r="P29" s="334">
         <v>2.76</v>
       </c>
-      <c r="Q29" s="335">
+      <c r="Q29" s="333">
         <v>-3.56</v>
       </c>
-      <c r="R29" s="336">
+      <c r="R29" s="335">
         <v>-8.22</v>
       </c>
-      <c r="S29" s="325">
+      <c r="S29" s="336">
         <v>-10.22</v>
       </c>
-      <c r="T29" s="327">
+      <c r="T29" s="325">
         <v>-2.62</v>
       </c>
     </row>
@@ -11429,40 +11429,40 @@
       <c r="H30">
         <v>0.97</v>
       </c>
-      <c r="I30" s="342">
+      <c r="I30" s="344">
         <v>5.31</v>
       </c>
-      <c r="J30" s="339">
+      <c r="J30" s="342">
         <v>8.18</v>
       </c>
-      <c r="K30" s="340">
+      <c r="K30" s="348">
         <v>-1.59</v>
       </c>
-      <c r="L30" s="341">
+      <c r="L30" s="345">
         <v>-6.27</v>
       </c>
-      <c r="M30" s="343">
+      <c r="M30" s="337">
         <v>-10.1</v>
       </c>
-      <c r="N30" s="344">
+      <c r="N30" s="338">
         <v>-7.76</v>
       </c>
-      <c r="O30" s="347">
+      <c r="O30" s="339">
         <v>-11.26</v>
       </c>
-      <c r="P30" s="345">
+      <c r="P30" s="340">
         <v>-12.33</v>
       </c>
-      <c r="Q30" s="346">
+      <c r="Q30" s="343">
         <v>-3.51</v>
       </c>
-      <c r="R30" s="348">
+      <c r="R30" s="346">
         <v>-4.78</v>
       </c>
-      <c r="S30" s="337">
+      <c r="S30" s="341">
         <v>-3.08</v>
       </c>
-      <c r="T30" s="338">
+      <c r="T30" s="347">
         <v>-27.74</v>
       </c>
     </row>
@@ -11491,40 +11491,40 @@
       <c r="H31">
         <v>1.37</v>
       </c>
-      <c r="I31" s="355">
+      <c r="I31" s="354">
         <v>5.49</v>
       </c>
-      <c r="J31" s="360">
+      <c r="J31" s="356">
         <v>16.03</v>
       </c>
-      <c r="K31" s="356">
+      <c r="K31" s="357">
         <v>11.44</v>
       </c>
-      <c r="L31" s="349">
+      <c r="L31" s="350">
         <v>16.78</v>
       </c>
-      <c r="M31" s="357">
+      <c r="M31" s="355">
         <v>5.34</v>
       </c>
-      <c r="N31" s="358">
+      <c r="N31" s="351">
         <v>3.91</v>
       </c>
-      <c r="O31" s="353">
+      <c r="O31" s="359">
         <v>5.27</v>
       </c>
-      <c r="P31" s="352">
+      <c r="P31" s="360">
         <v>-1.96</v>
       </c>
-      <c r="Q31" s="354">
+      <c r="Q31" s="358">
         <v>0.53</v>
       </c>
-      <c r="R31" s="359">
+      <c r="R31" s="352">
         <v>-5.49</v>
       </c>
-      <c r="S31" s="350">
+      <c r="S31" s="349">
         <v>-7.37</v>
       </c>
-      <c r="T31" s="351">
+      <c r="T31" s="353">
         <v>-14</v>
       </c>
     </row>
@@ -11553,7 +11553,7 @@
       <c r="H32">
         <v>0.91</v>
       </c>
-      <c r="I32" s="364">
+      <c r="I32" s="369">
         <v>1.8</v>
       </c>
       <c r="J32" s="371">
@@ -11562,31 +11562,31 @@
       <c r="K32" s="372">
         <v>-11.8</v>
       </c>
-      <c r="L32" s="365">
+      <c r="L32" s="361">
         <v>-15.4</v>
       </c>
       <c r="M32" s="366">
         <v>-13.2</v>
       </c>
-      <c r="N32" s="369">
+      <c r="N32" s="362">
         <v>-16.5</v>
       </c>
-      <c r="O32" s="370">
+      <c r="O32" s="363">
         <v>-17.5</v>
       </c>
-      <c r="P32" s="367">
+      <c r="P32" s="364">
         <v>-9.2</v>
       </c>
-      <c r="Q32" s="361">
+      <c r="Q32" s="367">
         <v>-10.4</v>
       </c>
-      <c r="R32" s="368">
+      <c r="R32" s="370">
         <v>-8.8</v>
       </c>
-      <c r="S32" s="362">
+      <c r="S32" s="368">
         <v>-6.6</v>
       </c>
-      <c r="T32" s="363">
+      <c r="T32" s="365">
         <v>-32</v>
       </c>
     </row>
@@ -11615,40 +11615,40 @@
       <c r="H33">
         <v>3.37</v>
       </c>
-      <c r="I33" s="380">
+      <c r="I33" s="382">
         <v>-2.9</v>
       </c>
-      <c r="J33" s="382">
+      <c r="J33" s="383">
         <v>-4.39</v>
       </c>
-      <c r="K33" s="376">
+      <c r="K33" s="380">
         <v>-9.32</v>
       </c>
-      <c r="L33" s="383">
+      <c r="L33" s="376">
         <v>-9.35</v>
       </c>
-      <c r="M33" s="377">
+      <c r="M33" s="381">
         <v>-14.85</v>
       </c>
-      <c r="N33" s="381">
+      <c r="N33" s="384">
         <v>-16.34</v>
       </c>
-      <c r="O33" s="384">
+      <c r="O33" s="377">
         <v>-15.09</v>
       </c>
-      <c r="P33" s="373">
+      <c r="P33" s="374">
         <v>-16.04</v>
       </c>
       <c r="Q33" s="378">
         <v>-17.6</v>
       </c>
-      <c r="R33" s="374">
+      <c r="R33" s="379">
         <v>-9.35</v>
       </c>
-      <c r="S33" s="375">
+      <c r="S33" s="373">
         <v>-8.16</v>
       </c>
-      <c r="T33" s="379">
+      <c r="T33" s="375">
         <v>-24.29</v>
       </c>
     </row>
@@ -11677,40 +11677,40 @@
       <c r="H34">
         <v>1.81</v>
       </c>
-      <c r="I34" s="396">
+      <c r="I34" s="388">
         <v>8.09</v>
       </c>
-      <c r="J34" s="385">
+      <c r="J34" s="391">
         <v>5.96</v>
       </c>
-      <c r="K34" s="391">
+      <c r="K34" s="389">
         <v>4.82</v>
       </c>
-      <c r="L34" s="386">
+      <c r="L34" s="395">
         <v>-0.57</v>
       </c>
-      <c r="M34" s="392">
+      <c r="M34" s="390">
         <v>-6.03</v>
       </c>
-      <c r="N34" s="387">
+      <c r="N34" s="396">
         <v>-8.37</v>
       </c>
-      <c r="O34" s="388">
+      <c r="O34" s="385">
         <v>-4.75</v>
       </c>
-      <c r="P34" s="393">
+      <c r="P34" s="392">
         <v>2.41</v>
       </c>
-      <c r="Q34" s="389">
+      <c r="Q34" s="386">
         <v>1.28</v>
       </c>
-      <c r="R34" s="390">
+      <c r="R34" s="393">
         <v>-0.07</v>
       </c>
-      <c r="S34" s="394">
+      <c r="S34" s="387">
         <v>-2.55</v>
       </c>
-      <c r="T34" s="395">
+      <c r="T34" s="394">
         <v>53.62</v>
       </c>
     </row>
@@ -11739,40 +11739,40 @@
       <c r="H35">
         <v>-3</v>
       </c>
-      <c r="I35" s="397">
+      <c r="I35" s="408">
         <v>-7.21</v>
       </c>
-      <c r="J35" s="406">
+      <c r="J35" s="403">
         <v>-5.8</v>
       </c>
-      <c r="K35" s="398">
+      <c r="K35" s="404">
         <v>-7.63</v>
       </c>
-      <c r="L35" s="405">
+      <c r="L35" s="397">
         <v>-15.49</v>
       </c>
-      <c r="M35" s="399">
+      <c r="M35" s="405">
         <v>-23.94</v>
       </c>
-      <c r="N35" s="402">
+      <c r="N35" s="406">
         <v>-20.49</v>
       </c>
-      <c r="O35" s="407">
+      <c r="O35" s="398">
         <v>-25.23</v>
       </c>
-      <c r="P35" s="403">
+      <c r="P35" s="399">
         <v>-22.56</v>
       </c>
       <c r="Q35" s="400">
         <v>-25.72</v>
       </c>
-      <c r="R35" s="408">
+      <c r="R35" s="401">
         <v>-26.94</v>
       </c>
-      <c r="S35" s="401">
+      <c r="S35" s="407">
         <v>-26.81</v>
       </c>
-      <c r="T35" s="404">
+      <c r="T35" s="402">
         <v>-44.84</v>
       </c>
     </row>
@@ -11801,40 +11801,40 @@
       <c r="H36">
         <v>5.94</v>
       </c>
-      <c r="I36" s="411">
+      <c r="I36" s="413">
         <v>3.84</v>
       </c>
-      <c r="J36" s="412">
+      <c r="J36" s="414">
         <v>-6.54</v>
       </c>
-      <c r="K36" s="415">
+      <c r="K36" s="410">
         <v>-15.9</v>
       </c>
-      <c r="L36" s="418">
+      <c r="L36" s="411">
         <v>-16.95</v>
       </c>
-      <c r="M36" s="419">
+      <c r="M36" s="415">
         <v>-17.11</v>
       </c>
-      <c r="N36" s="416">
+      <c r="N36" s="418">
         <v>-23.13</v>
       </c>
-      <c r="O36" s="413">
+      <c r="O36" s="419">
         <v>-26.61</v>
       </c>
-      <c r="P36" s="417">
+      <c r="P36" s="420">
         <v>-26.41</v>
       </c>
-      <c r="Q36" s="414">
+      <c r="Q36" s="416">
         <v>-24.65</v>
       </c>
-      <c r="R36" s="409">
+      <c r="R36" s="417">
         <v>-24.54</v>
       </c>
-      <c r="S36" s="410">
+      <c r="S36" s="412">
         <v>-24.32</v>
       </c>
-      <c r="T36" s="420">
+      <c r="T36" s="409">
         <v>-27.77</v>
       </c>
     </row>
@@ -11863,40 +11863,40 @@
       <c r="H37">
         <v>1.86</v>
       </c>
-      <c r="I37" s="425">
+      <c r="I37" s="427">
         <v>-7.6</v>
       </c>
-      <c r="J37" s="431">
+      <c r="J37" s="428">
         <v>-2.8</v>
       </c>
-      <c r="K37" s="432">
+      <c r="K37" s="429">
         <v>6.09</v>
       </c>
-      <c r="L37" s="426">
+      <c r="L37" s="430">
         <v>10.62</v>
       </c>
-      <c r="M37" s="422">
+      <c r="M37" s="431">
         <v>4.62</v>
       </c>
-      <c r="N37" s="429">
+      <c r="N37" s="423">
         <v>15.1</v>
       </c>
-      <c r="O37" s="421">
+      <c r="O37" s="432">
         <v>12.08</v>
       </c>
-      <c r="P37" s="430">
+      <c r="P37" s="424">
         <v>6.89</v>
       </c>
-      <c r="Q37" s="427">
+      <c r="Q37" s="421">
         <v>17.59</v>
       </c>
-      <c r="R37" s="423">
+      <c r="R37" s="425">
         <v>24.57</v>
       </c>
-      <c r="S37" s="428">
+      <c r="S37" s="426">
         <v>28.83</v>
       </c>
-      <c r="T37" s="424">
+      <c r="T37" s="422">
         <v>-3.64</v>
       </c>
     </row>
@@ -11925,40 +11925,40 @@
       <c r="H38">
         <v>-1.77</v>
       </c>
-      <c r="I38" s="440">
+      <c r="I38" s="443">
         <v>-4.39</v>
       </c>
-      <c r="J38" s="441">
+      <c r="J38" s="444">
         <v>2.66</v>
       </c>
-      <c r="K38" s="442">
+      <c r="K38" s="441">
         <v>3.96</v>
       </c>
-      <c r="L38" s="434">
+      <c r="L38" s="435">
         <v>14.33</v>
       </c>
-      <c r="M38" s="435">
+      <c r="M38" s="439">
         <v>14.83</v>
       </c>
-      <c r="N38" s="437">
+      <c r="N38" s="442">
         <v>13.82</v>
       </c>
-      <c r="O38" s="443">
+      <c r="O38" s="436">
         <v>19.44</v>
       </c>
-      <c r="P38" s="444">
+      <c r="P38" s="433">
         <v>23.54</v>
       </c>
-      <c r="Q38" s="438">
+      <c r="Q38" s="440">
         <v>11.16</v>
       </c>
-      <c r="R38" s="439">
+      <c r="R38" s="437">
         <v>0.07</v>
       </c>
-      <c r="S38" s="433">
+      <c r="S38" s="438">
         <v>0.07</v>
       </c>
-      <c r="T38" s="436">
+      <c r="T38" s="434">
         <v>18</v>
       </c>
     </row>
@@ -11987,40 +11987,40 @@
       <c r="H39">
         <v>0.25</v>
       </c>
-      <c r="I39" s="450">
+      <c r="I39" s="445">
         <v>1.06</v>
       </c>
-      <c r="J39" s="446">
+      <c r="J39" s="453">
         <v>-0.81</v>
       </c>
-      <c r="K39" s="447">
+      <c r="K39" s="446">
         <v>-2.94</v>
       </c>
-      <c r="L39" s="451">
+      <c r="L39" s="450">
         <v>-1.31</v>
       </c>
-      <c r="M39" s="452">
+      <c r="M39" s="451">
         <v>-2.56</v>
       </c>
-      <c r="N39" s="448">
+      <c r="N39" s="447">
         <v>0.44</v>
       </c>
-      <c r="O39" s="449">
+      <c r="O39" s="454">
         <v>-3.44</v>
       </c>
-      <c r="P39" s="454">
+      <c r="P39" s="455">
         <v>-13.12</v>
       </c>
-      <c r="Q39" s="455">
+      <c r="Q39" s="448">
         <v>-21.8</v>
       </c>
       <c r="R39" s="456">
         <v>-19.43</v>
       </c>
-      <c r="S39" s="445">
+      <c r="S39" s="449">
         <v>-18.68</v>
       </c>
-      <c r="T39" s="453">
+      <c r="T39" s="452">
         <v>-21.24</v>
       </c>
     </row>
@@ -12049,40 +12049,40 @@
       <c r="H40">
         <v>-0.63</v>
       </c>
-      <c r="I40" s="465">
+      <c r="I40" s="466">
         <v>-2.69</v>
       </c>
-      <c r="J40" s="467">
+      <c r="J40" s="460">
         <v>-9.6</v>
       </c>
-      <c r="K40" s="468">
+      <c r="K40" s="467">
         <v>-8.57</v>
       </c>
-      <c r="L40" s="459">
+      <c r="L40" s="468">
         <v>-8.94</v>
       </c>
-      <c r="M40" s="460">
+      <c r="M40" s="457">
         <v>-4.65</v>
       </c>
-      <c r="N40" s="461">
+      <c r="N40" s="458">
         <v>-6.59</v>
       </c>
-      <c r="O40" s="466">
+      <c r="O40" s="462">
         <v>-12.86</v>
       </c>
-      <c r="P40" s="457">
+      <c r="P40" s="461">
         <v>-16.02</v>
       </c>
-      <c r="Q40" s="462">
+      <c r="Q40" s="463">
         <v>-14.33</v>
       </c>
-      <c r="R40" s="458">
+      <c r="R40" s="464">
         <v>-12.49</v>
       </c>
-      <c r="S40" s="463">
+      <c r="S40" s="459">
         <v>-17.56</v>
       </c>
-      <c r="T40" s="464">
+      <c r="T40" s="465">
         <v>-6.17</v>
       </c>
     </row>
@@ -12117,34 +12117,34 @@
       <c r="J41" s="474">
         <v>-15.32</v>
       </c>
-      <c r="K41" s="478">
+      <c r="K41" s="475">
         <v>-17.44</v>
       </c>
-      <c r="L41" s="475">
+      <c r="L41" s="469">
         <v>-13.75</v>
       </c>
       <c r="M41" s="470">
         <v>-12.79</v>
       </c>
-      <c r="N41" s="479">
+      <c r="N41" s="476">
         <v>-21.49</v>
       </c>
-      <c r="O41" s="469">
+      <c r="O41" s="479">
         <v>-22.75</v>
       </c>
-      <c r="P41" s="476">
+      <c r="P41" s="477">
         <v>-24.62</v>
       </c>
-      <c r="Q41" s="471">
+      <c r="Q41" s="478">
         <v>-28.06</v>
       </c>
-      <c r="R41" s="472">
+      <c r="R41" s="471">
         <v>-25.68</v>
       </c>
-      <c r="S41" s="473">
+      <c r="S41" s="472">
         <v>-28.61</v>
       </c>
-      <c r="T41" s="477">
+      <c r="T41" s="473">
         <v>-34.28</v>
       </c>
     </row>
@@ -12173,40 +12173,40 @@
       <c r="H42">
         <v>-7.05</v>
       </c>
-      <c r="I42" s="491">
+      <c r="I42" s="487">
         <v>11.04</v>
       </c>
-      <c r="J42" s="492">
+      <c r="J42" s="484">
         <v>0</v>
       </c>
-      <c r="K42" s="483">
+      <c r="K42" s="492">
         <v>-2.39</v>
       </c>
-      <c r="L42" s="487">
+      <c r="L42" s="485">
         <v>-5.85</v>
       </c>
-      <c r="M42" s="484">
+      <c r="M42" s="481">
         <v>0</v>
       </c>
-      <c r="N42" s="481">
+      <c r="N42" s="488">
         <v>2.13</v>
       </c>
-      <c r="O42" s="488">
+      <c r="O42" s="489">
         <v>-5.05</v>
       </c>
-      <c r="P42" s="485">
+      <c r="P42" s="490">
         <v>-11.7</v>
       </c>
-      <c r="Q42" s="486">
+      <c r="Q42" s="482">
         <v>-2.93</v>
       </c>
-      <c r="R42" s="489">
+      <c r="R42" s="491">
         <v>6.78</v>
       </c>
-      <c r="S42" s="482">
+      <c r="S42" s="486">
         <v>7.05</v>
       </c>
-      <c r="T42" s="490">
+      <c r="T42" s="483">
         <v>34.57</v>
       </c>
     </row>
@@ -12235,40 +12235,40 @@
       <c r="H43">
         <v>3.03</v>
       </c>
-      <c r="I43" s="504">
+      <c r="I43" s="499">
         <v>0</v>
       </c>
-      <c r="J43" s="497">
+      <c r="J43" s="494">
         <v>1.71</v>
       </c>
-      <c r="K43" s="493">
+      <c r="K43" s="495">
         <v>-7.41</v>
       </c>
-      <c r="L43" s="500">
+      <c r="L43" s="503">
         <v>-10.29</v>
       </c>
-      <c r="M43" s="498">
+      <c r="M43" s="493">
         <v>-1.29</v>
       </c>
-      <c r="N43" s="495">
+      <c r="N43" s="500">
         <v>-3.47</v>
       </c>
-      <c r="O43" s="501">
+      <c r="O43" s="496">
         <v>-3</v>
       </c>
-      <c r="P43" s="502">
+      <c r="P43" s="497">
         <v>-1.76</v>
       </c>
-      <c r="Q43" s="496">
+      <c r="Q43" s="501">
         <v>-0.88</v>
       </c>
-      <c r="R43" s="503">
+      <c r="R43" s="498">
         <v>9.06</v>
       </c>
-      <c r="S43" s="499">
+      <c r="S43" s="502">
         <v>13.29</v>
       </c>
-      <c r="T43" s="494">
+      <c r="T43" s="504">
         <v>27.41</v>
       </c>
     </row>
@@ -12297,40 +12297,40 @@
       <c r="H44">
         <v>-0.8</v>
       </c>
-      <c r="I44" s="505">
+      <c r="I44" s="514">
         <v>-1.61</v>
       </c>
-      <c r="J44" s="506">
+      <c r="J44" s="515">
         <v>-5.09</v>
       </c>
-      <c r="K44" s="511">
+      <c r="K44" s="509">
         <v>0.8</v>
       </c>
-      <c r="L44" s="515">
+      <c r="L44" s="510">
         <v>2.95</v>
       </c>
-      <c r="M44" s="512">
+      <c r="M44" s="511">
         <v>-4.29</v>
       </c>
-      <c r="N44" s="507">
+      <c r="N44" s="505">
         <v>-10.99</v>
       </c>
-      <c r="O44" s="513">
+      <c r="O44" s="506">
         <v>-2.14</v>
       </c>
-      <c r="P44" s="508">
+      <c r="P44" s="513">
         <v>7.64</v>
       </c>
-      <c r="Q44" s="509">
+      <c r="Q44" s="512">
         <v>7.91</v>
       </c>
-      <c r="R44" s="514">
+      <c r="R44" s="507">
         <v>-2.28</v>
       </c>
-      <c r="S44" s="516">
+      <c r="S44" s="508">
         <v>-4.29</v>
       </c>
-      <c r="T44" s="510">
+      <c r="T44" s="516">
         <v>35.66</v>
       </c>
     </row>
@@ -12359,38 +12359,38 @@
       <c r="H45">
         <v>3.19</v>
       </c>
-      <c r="I45" s="521">
+      <c r="I45" s="522">
         <v>1.28</v>
       </c>
-      <c r="J45" s="522">
+      <c r="J45" s="527">
         <v>11.43</v>
       </c>
       <c r="K45" s="523">
         <v>14.73</v>
       </c>
-      <c r="L45" s="526">
+      <c r="L45" s="517">
         <v>14.86</v>
       </c>
-      <c r="M45" s="527">
+      <c r="M45" s="524">
         <v>26.36</v>
       </c>
-      <c r="N45" s="519">
+      <c r="N45" s="518">
         <v>15</v>
       </c>
-      <c r="O45" s="520">
+      <c r="O45" s="519">
         <v>17.69</v>
       </c>
-      <c r="P45" s="517">
+      <c r="P45" s="520">
         <v>20.85</v>
       </c>
-      <c r="Q45" s="524">
+      <c r="Q45" s="525">
         <v>12.64</v>
       </c>
-      <c r="R45" s="525">
+      <c r="R45" s="526">
         <v>10.22</v>
       </c>
       <c r="S45" t="str"/>
-      <c r="T45" s="518">
+      <c r="T45" s="521">
         <v>10.22</v>
       </c>
     </row>
@@ -12419,31 +12419,31 @@
       <c r="H46">
         <v>6.57</v>
       </c>
-      <c r="I46" s="528">
+      <c r="I46" s="529">
         <v>3.23</v>
       </c>
-      <c r="J46" s="529">
+      <c r="J46" s="535">
         <v>13.56</v>
       </c>
-      <c r="K46" s="533">
+      <c r="K46" s="532">
         <v>24.92</v>
       </c>
-      <c r="L46" s="535">
+      <c r="L46" s="537">
         <v>34.8</v>
       </c>
-      <c r="M46" s="536">
+      <c r="M46" s="528">
         <v>21.32</v>
       </c>
       <c r="N46" s="530">
         <v>9.19</v>
       </c>
-      <c r="O46" s="537">
+      <c r="O46" s="533">
         <v>10.17</v>
       </c>
       <c r="P46" s="531">
         <v>13.15</v>
       </c>
-      <c r="Q46" s="532">
+      <c r="Q46" s="536">
         <v>17.73</v>
       </c>
       <c r="R46" t="str"/>
@@ -12477,19 +12477,19 @@
       <c r="H47">
         <v>-3.47</v>
       </c>
-      <c r="I47" s="541">
+      <c r="I47" s="540">
         <v>11.54</v>
       </c>
-      <c r="J47" s="542">
+      <c r="J47" s="541">
         <v>16.51</v>
       </c>
-      <c r="K47" s="543">
+      <c r="K47" s="542">
         <v>28.13</v>
       </c>
-      <c r="L47" s="538">
+      <c r="L47" s="543">
         <v>24.16</v>
       </c>
-      <c r="M47" s="539">
+      <c r="M47" s="538">
         <v>26.22</v>
       </c>
       <c r="N47" t="str"/>
@@ -12498,7 +12498,7 @@
       <c r="Q47" t="str"/>
       <c r="R47" t="str"/>
       <c r="S47" t="str"/>
-      <c r="T47" s="540">
+      <c r="T47" s="539">
         <v>26.22</v>
       </c>
     </row>
@@ -12577,19 +12577,19 @@
       <c r="H49">
         <v>-0.16</v>
       </c>
-      <c r="I49" s="555">
+      <c r="I49" s="554">
         <v>-1.41</v>
       </c>
-      <c r="J49" s="550">
+      <c r="J49" s="555">
         <v>2.5</v>
       </c>
-      <c r="K49" s="551">
+      <c r="K49" s="550">
         <v>5.31</v>
       </c>
-      <c r="L49" s="552">
+      <c r="L49" s="551">
         <v>-4.38</v>
       </c>
-      <c r="M49" s="553">
+      <c r="M49" s="552">
         <v>-12.19</v>
       </c>
       <c r="N49" t="str"/>
@@ -12598,7 +12598,7 @@
       <c r="Q49" t="str"/>
       <c r="R49" t="str"/>
       <c r="S49" t="str"/>
-      <c r="T49" s="554">
+      <c r="T49" s="553">
         <v>-12.19</v>
       </c>
     </row>
@@ -12701,40 +12701,40 @@
       <c r="F52" t="str"/>
       <c r="G52" t="str"/>
       <c r="H52" t="str"/>
-      <c r="I52" s="562">
+      <c r="I52" s="566">
         <v>67.35</v>
       </c>
-      <c r="J52" s="568">
+      <c r="J52" s="560">
         <v>60.42</v>
       </c>
-      <c r="K52" s="563">
+      <c r="K52" s="562">
         <v>56.25</v>
       </c>
-      <c r="L52" s="559">
+      <c r="L52" s="564">
         <v>54.17</v>
       </c>
-      <c r="M52" s="557">
+      <c r="M52" s="567">
         <v>47.92</v>
       </c>
-      <c r="N52" s="564">
+      <c r="N52" s="565">
         <v>53.33</v>
       </c>
-      <c r="O52" s="558">
+      <c r="O52" s="568">
         <v>51.11</v>
       </c>
-      <c r="P52" s="566">
+      <c r="P52" s="563">
         <v>51.11</v>
       </c>
-      <c r="Q52" s="565">
+      <c r="Q52" s="561">
         <v>51.11</v>
       </c>
-      <c r="R52" s="567">
+      <c r="R52" s="557">
         <v>50</v>
       </c>
-      <c r="S52" s="560">
+      <c r="S52" s="558">
         <v>41.86</v>
       </c>
-      <c r="T52" s="561">
+      <c r="T52" s="559">
         <v>41.67</v>
       </c>
     </row>
@@ -12749,40 +12749,40 @@
       <c r="F53" t="str"/>
       <c r="G53" t="str"/>
       <c r="H53" t="str"/>
-      <c r="I53" s="574">
+      <c r="I53" s="576">
         <v>2.72</v>
       </c>
-      <c r="J53" s="571">
+      <c r="J53" s="579">
         <v>3.16</v>
       </c>
-      <c r="K53" s="578">
+      <c r="K53" s="570">
         <v>3.1</v>
       </c>
-      <c r="L53" s="580">
+      <c r="L53" s="572">
         <v>2.29</v>
       </c>
-      <c r="M53" s="579">
+      <c r="M53" s="571">
         <v>2.22</v>
       </c>
-      <c r="N53" s="575">
+      <c r="N53" s="573">
         <v>0.76</v>
       </c>
-      <c r="O53" s="572">
+      <c r="O53" s="577">
         <v>0.64</v>
       </c>
-      <c r="P53" s="573">
+      <c r="P53" s="578">
         <v>1.2</v>
       </c>
-      <c r="Q53" s="569">
+      <c r="Q53" s="580">
         <v>0.07</v>
       </c>
-      <c r="R53" s="576">
+      <c r="R53" s="574">
         <v>-0.67</v>
       </c>
-      <c r="S53" s="570">
+      <c r="S53" s="569">
         <v>-1.34</v>
       </c>
-      <c r="T53" s="577">
+      <c r="T53" s="575">
         <v>-1.01</v>
       </c>
     </row>

--- a/youzi/老中医/index.xlsx
+++ b/youzi/老中医/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="582">
+  <fills count="589">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,13 +39,1963 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B0B6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BE77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DCB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D9DC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA849"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7DC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6737E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3C4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA1A9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,61 +2007,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DADD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF68C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD93343"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,19 +2199,1201 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3C4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,61 +3405,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,475 +3489,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B0B6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFEA858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -691,2834 +3559,57 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DCB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA849"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D9DC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7DC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6737E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4756"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DADD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA1A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF68C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3C4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BE77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="581">
+  <borders count="588">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7590,7 +7681,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="581">
+  <cellXfs count="588">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -9330,6 +9421,27 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="580" fillId="581" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="581" fillId="582" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="582" fillId="583" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="583" fillId="584" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="584" fillId="585" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="585" fillId="586" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="586" fillId="587" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="587" fillId="588" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -9689,13 +9801,13 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="9">
         <v>3.21</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="1">
         <v>13.58</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="3">
         <v>10.09</v>
       </c>
       <c r="L2" s="10">
@@ -9707,7 +9819,7 @@
       <c r="N2" s="11">
         <v>7.71</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="2">
         <v>7.43</v>
       </c>
       <c r="P2" s="12">
@@ -9716,14 +9828,14 @@
       <c r="Q2" s="5">
         <v>3.67</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="7">
         <v>2.75</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="6">
         <v>-1.38</v>
       </c>
-      <c r="T2" s="1">
-        <v>-38.17</v>
+      <c r="T2" s="8">
+        <v>-38.72</v>
       </c>
     </row>
     <row r="3">
@@ -9751,41 +9863,41 @@
       <c r="H3">
         <v>1.53</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="14">
         <v>8.3</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="22">
         <v>12.74</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="15">
         <v>3.87</v>
       </c>
       <c r="L3" s="23">
         <v>6.42</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="16">
         <v>11.13</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="21">
         <v>22.26</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="17">
         <v>23.58</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="18">
         <v>28.87</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="24">
         <v>33.3</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="19">
         <v>27.64</v>
       </c>
-      <c r="S3" s="13">
+      <c r="S3" s="20">
         <v>20.09</v>
       </c>
-      <c r="T3" s="14">
-        <v>-21.32</v>
+      <c r="T3" s="13">
+        <v>-23.4</v>
       </c>
     </row>
     <row r="4">
@@ -9813,41 +9925,41 @@
       <c r="H4">
         <v>-3.75</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="32">
         <v>8.14</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="26">
         <v>-0.36</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="36">
         <v>2.08</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="27">
         <v>6.61</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="33">
         <v>17.29</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="25">
         <v>18.55</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="28">
         <v>23.62</v>
       </c>
-      <c r="P4" s="26">
+      <c r="P4" s="29">
         <v>27.87</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="30">
         <v>22.44</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="31">
         <v>15.2</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="34">
         <v>12.58</v>
       </c>
-      <c r="T4" s="27">
-        <v>-24.52</v>
+      <c r="T4" s="35">
+        <v>-26.52</v>
       </c>
     </row>
     <row r="5">
@@ -9875,41 +9987,41 @@
       <c r="H5">
         <v>-0.83</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="43">
         <v>-5.04</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="40">
         <v>-5.88</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="37">
         <v>-9.66</v>
       </c>
-      <c r="L5" s="39">
+      <c r="L5" s="41">
         <v>-8.82</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="38">
         <v>-12.02</v>
       </c>
-      <c r="N5" s="37">
+      <c r="N5" s="44">
         <v>-12.61</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="45">
         <v>-16.22</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="39">
         <v>-15.13</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="46">
         <v>-16.89</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="42">
         <v>-16.22</v>
       </c>
-      <c r="S5" s="38">
+      <c r="S5" s="47">
         <v>-15.13</v>
       </c>
-      <c r="T5" s="44">
-        <v>-43.36</v>
+      <c r="T5" s="48">
+        <v>-43.87</v>
       </c>
     </row>
     <row r="6">
@@ -9937,41 +10049,41 @@
       <c r="H6">
         <v>-0.24</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="49">
         <v>-2.16</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="53">
         <v>-2.4</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="50">
         <v>-5.05</v>
       </c>
-      <c r="L6" s="49">
+      <c r="L6" s="51">
         <v>-3.37</v>
       </c>
-      <c r="M6" s="50">
+      <c r="M6" s="57">
         <v>-4.81</v>
       </c>
-      <c r="N6" s="51">
+      <c r="N6" s="60">
         <v>-1.2</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="54">
         <v>-3.85</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="58">
         <v>-2.64</v>
       </c>
-      <c r="Q6" s="52">
+      <c r="Q6" s="55">
         <v>0.48</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="56">
         <v>0.24</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="59">
         <v>-0.24</v>
       </c>
-      <c r="T6" s="54">
-        <v>33.41</v>
+      <c r="T6" s="52">
+        <v>31.73</v>
       </c>
     </row>
     <row r="7">
@@ -9999,41 +10111,41 @@
       <c r="H7">
         <v>-1.58</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="62">
         <v>7.2</v>
       </c>
-      <c r="J7" s="63">
+      <c r="J7" s="67">
         <v>9.53</v>
       </c>
-      <c r="K7" s="64">
+      <c r="K7" s="63">
         <v>10.1</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="66">
         <v>11.2</v>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="68">
         <v>15.78</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="71">
         <v>11.36</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="64">
         <v>11.51</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="69">
         <v>22.68</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="65">
         <v>13.03</v>
       </c>
-      <c r="R7" s="61">
+      <c r="R7" s="72">
         <v>13.07</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="70">
         <v>9.45</v>
       </c>
-      <c r="T7" s="62">
-        <v>44.05</v>
+      <c r="T7" s="61">
+        <v>40.59</v>
       </c>
     </row>
     <row r="8">
@@ -10064,38 +10176,38 @@
       <c r="I8" s="81">
         <v>1.94</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="73">
         <v>4.62</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="79">
         <v>-0.95</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="76">
         <v>0.22</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="77">
         <v>7.42</v>
       </c>
-      <c r="N8" s="73">
+      <c r="N8" s="74">
         <v>13.89</v>
       </c>
-      <c r="O8" s="76">
+      <c r="O8" s="82">
         <v>15.44</v>
       </c>
-      <c r="P8" s="74">
+      <c r="P8" s="83">
         <v>27.01</v>
       </c>
-      <c r="Q8" s="77">
+      <c r="Q8" s="75">
         <v>27.22</v>
       </c>
-      <c r="R8" s="75">
+      <c r="R8" s="84">
         <v>15.14</v>
       </c>
-      <c r="S8" s="78">
+      <c r="S8" s="80">
         <v>10.7</v>
       </c>
-      <c r="T8" s="79">
-        <v>-23.94</v>
+      <c r="T8" s="78">
+        <v>-27.44</v>
       </c>
     </row>
     <row r="9">
@@ -10123,41 +10235,41 @@
       <c r="H9">
         <v>-1.7</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="86">
         <v>0.24</v>
       </c>
-      <c r="J9" s="94">
+      <c r="J9" s="87">
         <v>1.92</v>
       </c>
-      <c r="K9" s="85">
+      <c r="K9" s="93">
         <v>-2.26</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="88">
         <v>-1.76</v>
       </c>
-      <c r="M9" s="90">
+      <c r="M9" s="94">
         <v>-1.81</v>
       </c>
       <c r="N9" s="95">
         <v>-0.43</v>
       </c>
-      <c r="O9" s="86">
+      <c r="O9" s="96">
         <v>6.75</v>
       </c>
-      <c r="P9" s="87">
+      <c r="P9" s="89">
         <v>9.69</v>
       </c>
-      <c r="Q9" s="91">
+      <c r="Q9" s="85">
         <v>8.65</v>
       </c>
-      <c r="R9" s="88">
+      <c r="R9" s="90">
         <v>12.49</v>
       </c>
-      <c r="S9" s="89">
+      <c r="S9" s="91">
         <v>12.78</v>
       </c>
       <c r="T9" s="92">
-        <v>18.98</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="10">
@@ -10185,7 +10297,7 @@
       <c r="H10">
         <v>-0.24</v>
       </c>
-      <c r="I10" s="97">
+      <c r="I10" s="103">
         <v>1.92</v>
       </c>
       <c r="J10" s="104">
@@ -10197,29 +10309,29 @@
       <c r="L10" s="99">
         <v>-1.81</v>
       </c>
-      <c r="M10" s="100">
+      <c r="M10" s="105">
         <v>-0.43</v>
       </c>
       <c r="N10" s="107">
         <v>6.75</v>
       </c>
-      <c r="O10" s="101">
+      <c r="O10" s="108">
         <v>9.69</v>
       </c>
-      <c r="P10" s="98">
+      <c r="P10" s="100">
         <v>8.65</v>
       </c>
-      <c r="Q10" s="102">
+      <c r="Q10" s="101">
         <v>12.49</v>
       </c>
-      <c r="R10" s="105">
+      <c r="R10" s="97">
         <v>12.78</v>
       </c>
-      <c r="S10" s="103">
+      <c r="S10" s="98">
         <v>19.76</v>
       </c>
-      <c r="T10" s="108">
-        <v>18.98</v>
+      <c r="T10" s="102">
+        <v>16.67</v>
       </c>
     </row>
     <row r="11">
@@ -10247,41 +10359,41 @@
       <c r="H11">
         <v>3.83</v>
       </c>
-      <c r="I11" s="112">
+      <c r="I11" s="119">
         <v>5.97</v>
       </c>
-      <c r="J11" s="109">
+      <c r="J11" s="112">
         <v>5.54</v>
       </c>
-      <c r="K11" s="110">
+      <c r="K11" s="120">
         <v>1.42</v>
       </c>
-      <c r="L11" s="114">
+      <c r="L11" s="117">
         <v>4.12</v>
       </c>
-      <c r="M11" s="115">
+      <c r="M11" s="113">
         <v>9.38</v>
       </c>
-      <c r="N11" s="111">
+      <c r="N11" s="116">
         <v>11.65</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="109">
         <v>9.09</v>
       </c>
-      <c r="P11" s="113">
+      <c r="P11" s="118">
         <v>4.55</v>
       </c>
-      <c r="Q11" s="116">
+      <c r="Q11" s="114">
         <v>3.69</v>
       </c>
-      <c r="R11" s="117">
+      <c r="R11" s="115">
         <v>4.12</v>
       </c>
-      <c r="S11" s="118">
+      <c r="S11" s="110">
         <v>3.84</v>
       </c>
-      <c r="T11" s="120">
-        <v>32.81</v>
+      <c r="T11" s="111">
+        <v>30.4</v>
       </c>
     </row>
     <row r="12">
@@ -10309,41 +10421,41 @@
       <c r="H12">
         <v>1.24</v>
       </c>
-      <c r="I12" s="131">
+      <c r="I12" s="125">
         <v>0.19</v>
       </c>
-      <c r="J12" s="122">
+      <c r="J12" s="123">
         <v>10.2</v>
       </c>
-      <c r="K12" s="127">
+      <c r="K12" s="126">
         <v>15.11</v>
       </c>
-      <c r="L12" s="123">
+      <c r="L12" s="132">
         <v>9.35</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="130">
         <v>12.65</v>
       </c>
-      <c r="N12" s="129">
+      <c r="N12" s="121">
         <v>13.31</v>
       </c>
-      <c r="O12" s="124">
+      <c r="O12" s="127">
         <v>15.49</v>
       </c>
-      <c r="P12" s="128">
+      <c r="P12" s="124">
         <v>12.37</v>
       </c>
-      <c r="Q12" s="125">
+      <c r="Q12" s="122">
         <v>12.09</v>
       </c>
-      <c r="R12" s="130">
+      <c r="R12" s="128">
         <v>7.84</v>
       </c>
-      <c r="S12" s="126">
+      <c r="S12" s="129">
         <v>8.97</v>
       </c>
-      <c r="T12" s="121">
-        <v>-16.15</v>
+      <c r="T12" s="131">
+        <v>-18.41</v>
       </c>
     </row>
     <row r="13">
@@ -10371,41 +10483,41 @@
       <c r="H13">
         <v>0.12</v>
       </c>
-      <c r="I13" s="140">
+      <c r="I13" s="134">
         <v>9.88</v>
       </c>
-      <c r="J13" s="133">
+      <c r="J13" s="142">
         <v>16.74</v>
       </c>
-      <c r="K13" s="141">
+      <c r="K13" s="139">
         <v>13.25</v>
       </c>
-      <c r="L13" s="142">
+      <c r="L13" s="135">
         <v>7.57</v>
       </c>
       <c r="M13" s="143">
         <v>1.63</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="140">
         <v>2.04</v>
       </c>
-      <c r="O13" s="134">
+      <c r="O13" s="137">
         <v>3.78</v>
       </c>
-      <c r="P13" s="136">
+      <c r="P13" s="144">
         <v>0.24</v>
       </c>
       <c r="Q13" s="138">
         <v>-1.39</v>
       </c>
-      <c r="R13" s="137">
+      <c r="R13" s="133">
         <v>-1.48</v>
       </c>
-      <c r="S13" s="139">
+      <c r="S13" s="136">
         <v>-3.64</v>
       </c>
-      <c r="T13" s="135">
-        <v>-18.98</v>
+      <c r="T13" s="141">
+        <v>-20.28</v>
       </c>
     </row>
     <row r="14">
@@ -10433,13 +10545,13 @@
       <c r="H14">
         <v>-0.7</v>
       </c>
-      <c r="I14" s="149">
+      <c r="I14" s="150">
         <v>1.82</v>
       </c>
-      <c r="J14" s="155">
+      <c r="J14" s="156">
         <v>-2</v>
       </c>
-      <c r="K14" s="156">
+      <c r="K14" s="148">
         <v>-1.98</v>
       </c>
       <c r="L14" s="145">
@@ -10448,7 +10560,7 @@
       <c r="M14" s="151">
         <v>10.14</v>
       </c>
-      <c r="N14" s="147">
+      <c r="N14" s="154">
         <v>14.17</v>
       </c>
       <c r="O14" s="146">
@@ -10457,17 +10569,17 @@
       <c r="P14" s="152">
         <v>17.86</v>
       </c>
-      <c r="Q14" s="153">
+      <c r="Q14" s="155">
         <v>15.7</v>
       </c>
-      <c r="R14" s="154">
+      <c r="R14" s="149">
         <v>13.49</v>
       </c>
-      <c r="S14" s="150">
+      <c r="S14" s="153">
         <v>4.66</v>
       </c>
-      <c r="T14" s="148">
-        <v>-6.15</v>
+      <c r="T14" s="147">
+        <v>-7.22</v>
       </c>
     </row>
     <row r="15">
@@ -10498,38 +10610,38 @@
       <c r="I15" s="158">
         <v>-0.85</v>
       </c>
-      <c r="J15" s="164">
+      <c r="J15" s="167">
         <v>-10.76</v>
       </c>
-      <c r="K15" s="160">
+      <c r="K15" s="159">
         <v>-14.5</v>
       </c>
-      <c r="L15" s="159">
+      <c r="L15" s="160">
         <v>-17.38</v>
       </c>
-      <c r="M15" s="161">
+      <c r="M15" s="168">
         <v>-11.49</v>
       </c>
-      <c r="N15" s="165">
+      <c r="N15" s="161">
         <v>-16.08</v>
       </c>
-      <c r="O15" s="168">
+      <c r="O15" s="166">
         <v>-7.7</v>
       </c>
-      <c r="P15" s="166">
+      <c r="P15" s="157">
         <v>1.53</v>
       </c>
-      <c r="Q15" s="162">
+      <c r="Q15" s="165">
         <v>11.66</v>
       </c>
-      <c r="R15" s="167">
+      <c r="R15" s="162">
         <v>22.82</v>
       </c>
       <c r="S15" s="163">
         <v>17.95</v>
       </c>
-      <c r="T15" s="157">
-        <v>94.79</v>
+      <c r="T15" s="164">
+        <v>92.53</v>
       </c>
     </row>
     <row r="16">
@@ -10557,28 +10669,28 @@
       <c r="H16">
         <v>0.86</v>
       </c>
-      <c r="I16" s="173">
+      <c r="I16" s="172">
         <v>5.26</v>
       </c>
-      <c r="J16" s="177">
+      <c r="J16" s="175">
         <v>6.4</v>
       </c>
-      <c r="K16" s="171">
+      <c r="K16" s="176">
         <v>12.52</v>
       </c>
-      <c r="L16" s="178">
+      <c r="L16" s="173">
         <v>2.7</v>
       </c>
-      <c r="M16" s="179">
+      <c r="M16" s="177">
         <v>-7.54</v>
       </c>
-      <c r="N16" s="175">
+      <c r="N16" s="178">
         <v>-14.94</v>
       </c>
-      <c r="O16" s="180">
+      <c r="O16" s="179">
         <v>-13.09</v>
       </c>
-      <c r="P16" s="174">
+      <c r="P16" s="180">
         <v>-15.93</v>
       </c>
       <c r="Q16" s="169">
@@ -10587,11 +10699,11 @@
       <c r="R16" s="170">
         <v>-9.1</v>
       </c>
-      <c r="S16" s="176">
+      <c r="S16" s="174">
         <v>-8.25</v>
       </c>
-      <c r="T16" s="172">
-        <v>-37.41</v>
+      <c r="T16" s="171">
+        <v>-39.12</v>
       </c>
     </row>
     <row r="17">
@@ -10619,41 +10731,41 @@
       <c r="H17">
         <v>1.1</v>
       </c>
-      <c r="I17" s="192">
+      <c r="I17" s="190">
         <v>6.65</v>
       </c>
-      <c r="J17" s="181">
+      <c r="J17" s="192">
         <v>7.27</v>
       </c>
-      <c r="K17" s="186">
+      <c r="K17" s="187">
         <v>5.3</v>
       </c>
-      <c r="L17" s="190">
+      <c r="L17" s="181">
         <v>-3.58</v>
       </c>
-      <c r="M17" s="183">
+      <c r="M17" s="188">
         <v>-8.37</v>
       </c>
-      <c r="N17" s="184">
+      <c r="N17" s="182">
         <v>-13.99</v>
       </c>
-      <c r="O17" s="191">
+      <c r="O17" s="183">
         <v>-9.72</v>
       </c>
-      <c r="P17" s="187">
+      <c r="P17" s="184">
         <v>-9.62</v>
       </c>
       <c r="Q17" s="185">
         <v>-13.01</v>
       </c>
-      <c r="R17" s="188">
+      <c r="R17" s="189">
         <v>-9.84</v>
       </c>
-      <c r="S17" s="182">
+      <c r="S17" s="186">
         <v>-7.26</v>
       </c>
-      <c r="T17" s="189">
-        <v>-22.11</v>
+      <c r="T17" s="191">
+        <v>-24.94</v>
       </c>
     </row>
     <row r="18">
@@ -10681,41 +10793,41 @@
       <c r="H18">
         <v>1.07</v>
       </c>
-      <c r="I18" s="199">
+      <c r="I18" s="196">
         <v>6.93</v>
       </c>
-      <c r="J18" s="200">
+      <c r="J18" s="197">
         <v>11.13</v>
       </c>
-      <c r="K18" s="195">
+      <c r="K18" s="198">
         <v>13.33</v>
       </c>
-      <c r="L18" s="204">
+      <c r="L18" s="199">
         <v>4.5</v>
       </c>
-      <c r="M18" s="196">
+      <c r="M18" s="193">
         <v>-0.96</v>
       </c>
-      <c r="N18" s="197">
+      <c r="N18" s="194">
         <v>-7.85</v>
       </c>
-      <c r="O18" s="201">
+      <c r="O18" s="195">
         <v>1.38</v>
       </c>
-      <c r="P18" s="198">
+      <c r="P18" s="204">
         <v>-1.51</v>
       </c>
       <c r="Q18" s="202">
         <v>-0.6</v>
       </c>
-      <c r="R18" s="193">
+      <c r="R18" s="200">
         <v>5.78</v>
       </c>
-      <c r="S18" s="194">
+      <c r="S18" s="203">
         <v>7.69</v>
       </c>
-      <c r="T18" s="203">
-        <v>5.35</v>
+      <c r="T18" s="201">
+        <v>1.33</v>
       </c>
     </row>
     <row r="19">
@@ -10743,41 +10855,41 @@
       <c r="H19">
         <v>-3.11</v>
       </c>
-      <c r="I19" s="213">
+      <c r="I19" s="216">
         <v>13.55</v>
       </c>
-      <c r="J19" s="206">
+      <c r="J19" s="215">
         <v>24.91</v>
       </c>
-      <c r="K19" s="216">
+      <c r="K19" s="206">
         <v>37.43</v>
       </c>
-      <c r="L19" s="214">
+      <c r="L19" s="212">
         <v>23.65</v>
       </c>
-      <c r="M19" s="210">
+      <c r="M19" s="205">
         <v>11.25</v>
       </c>
-      <c r="N19" s="207">
+      <c r="N19" s="213">
         <v>14.01</v>
       </c>
-      <c r="O19" s="208">
+      <c r="O19" s="207">
         <v>7.23</v>
       </c>
-      <c r="P19" s="211">
+      <c r="P19" s="208">
         <v>11.94</v>
       </c>
-      <c r="Q19" s="212">
+      <c r="Q19" s="209">
         <v>23.19</v>
       </c>
-      <c r="R19" s="215">
+      <c r="R19" s="210">
         <v>30.54</v>
       </c>
-      <c r="S19" s="209">
+      <c r="S19" s="214">
         <v>43.63</v>
       </c>
-      <c r="T19" s="205">
-        <v>23.65</v>
+      <c r="T19" s="211">
+        <v>25.37</v>
       </c>
     </row>
     <row r="20">
@@ -10806,41 +10918,41 @@
       <c r="H20">
         <v>0.33</v>
       </c>
-      <c r="I20" s="218">
+      <c r="I20" s="219">
         <v>-4.25</v>
       </c>
-      <c r="J20" s="224">
+      <c r="J20" s="217">
         <v>-3.47</v>
       </c>
-      <c r="K20" s="219">
+      <c r="K20" s="220">
         <v>-11.03</v>
       </c>
-      <c r="L20" s="226">
+      <c r="L20" s="222">
         <v>-2.14</v>
       </c>
-      <c r="M20" s="227">
+      <c r="M20" s="225">
         <v>1.36</v>
       </c>
-      <c r="N20" s="220">
+      <c r="N20" s="218">
         <v>0.92</v>
       </c>
-      <c r="O20" s="228">
+      <c r="O20" s="223">
         <v>-0.69</v>
       </c>
-      <c r="P20" s="222">
+      <c r="P20" s="226">
         <v>-0.81</v>
       </c>
-      <c r="Q20" s="217">
+      <c r="Q20" s="227">
         <v>-4.89</v>
       </c>
-      <c r="R20" s="221">
+      <c r="R20" s="224">
         <v>-7.48</v>
       </c>
-      <c r="S20" s="223">
+      <c r="S20" s="228">
         <v>-11.67</v>
       </c>
-      <c r="T20" s="225">
-        <v>3.67</v>
+      <c r="T20" s="221">
+        <v>1.75</v>
       </c>
     </row>
     <row r="21">
@@ -10869,41 +10981,41 @@
       <c r="H21">
         <v>3.45</v>
       </c>
-      <c r="I21" s="229">
+      <c r="I21" s="236">
         <v>-1.4</v>
       </c>
       <c r="J21" s="237">
         <v>-5.96</v>
       </c>
-      <c r="K21" s="230">
+      <c r="K21" s="240">
         <v>-8.85</v>
       </c>
-      <c r="L21" s="235">
+      <c r="L21" s="238">
         <v>0.26</v>
       </c>
-      <c r="M21" s="238">
+      <c r="M21" s="239">
         <v>7.8</v>
       </c>
-      <c r="N21" s="231">
+      <c r="N21" s="229">
         <v>18.58</v>
       </c>
-      <c r="O21" s="239">
+      <c r="O21" s="231">
         <v>6.75</v>
       </c>
-      <c r="P21" s="236">
+      <c r="P21" s="233">
         <v>6.05</v>
       </c>
-      <c r="Q21" s="232">
+      <c r="Q21" s="234">
         <v>5.08</v>
       </c>
-      <c r="R21" s="233">
+      <c r="R21" s="230">
         <v>0.53</v>
       </c>
-      <c r="S21" s="234">
+      <c r="S21" s="232">
         <v>-3.42</v>
       </c>
-      <c r="T21" s="240">
-        <v>-15.95</v>
+      <c r="T21" s="235">
+        <v>-14.02</v>
       </c>
     </row>
     <row r="22">
@@ -10932,41 +11044,41 @@
       <c r="H22">
         <v>-3.71</v>
       </c>
-      <c r="I22" s="252">
+      <c r="I22" s="241">
         <v>-1.57</v>
       </c>
-      <c r="J22" s="248">
+      <c r="J22" s="247">
         <v>-11.43</v>
       </c>
-      <c r="K22" s="247">
+      <c r="K22" s="242">
         <v>-20.29</v>
       </c>
-      <c r="L22" s="241">
+      <c r="L22" s="243">
         <v>-20.43</v>
       </c>
-      <c r="M22" s="242">
+      <c r="M22" s="248">
         <v>-23.79</v>
       </c>
       <c r="N22" s="249">
         <v>-23.86</v>
       </c>
-      <c r="O22" s="243">
+      <c r="O22" s="244">
         <v>-20.14</v>
       </c>
-      <c r="P22" s="244">
+      <c r="P22" s="245">
         <v>-20.57</v>
       </c>
-      <c r="Q22" s="245">
+      <c r="Q22" s="250">
         <v>-19.71</v>
       </c>
-      <c r="R22" s="250">
+      <c r="R22" s="251">
         <v>-17.86</v>
       </c>
-      <c r="S22" s="251">
+      <c r="S22" s="252">
         <v>-13.57</v>
       </c>
       <c r="T22" s="246">
-        <v>-9.93</v>
+        <v>-8.64</v>
       </c>
     </row>
     <row r="23">
@@ -10994,10 +11106,10 @@
       <c r="H23">
         <v>-1.94</v>
       </c>
-      <c r="I23" s="257">
+      <c r="I23" s="253">
         <v>-0.19</v>
       </c>
-      <c r="J23" s="261">
+      <c r="J23" s="254">
         <v>2.17</v>
       </c>
       <c r="K23" s="258">
@@ -11006,29 +11118,29 @@
       <c r="L23" s="262">
         <v>-3.02</v>
       </c>
-      <c r="M23" s="263">
+      <c r="M23" s="255">
         <v>-8.11</v>
       </c>
-      <c r="N23" s="264">
+      <c r="N23" s="259">
         <v>-10.74</v>
       </c>
-      <c r="O23" s="259">
+      <c r="O23" s="260">
         <v>-13.2</v>
       </c>
-      <c r="P23" s="253">
+      <c r="P23" s="256">
         <v>-12.72</v>
       </c>
-      <c r="Q23" s="254">
+      <c r="Q23" s="257">
         <v>-15.55</v>
       </c>
-      <c r="R23" s="256">
+      <c r="R23" s="261">
         <v>-14.99</v>
       </c>
-      <c r="S23" s="255">
+      <c r="S23" s="263">
         <v>-14.61</v>
       </c>
-      <c r="T23" s="260">
-        <v>-23.09</v>
+      <c r="T23" s="264">
+        <v>-23.66</v>
       </c>
     </row>
     <row r="24">
@@ -11056,41 +11168,41 @@
       <c r="H24">
         <v>5.07</v>
       </c>
-      <c r="I24" s="271">
+      <c r="I24" s="267">
         <v>4.74</v>
       </c>
-      <c r="J24" s="273">
+      <c r="J24" s="271">
         <v>8.49</v>
       </c>
       <c r="K24" s="274">
         <v>19.3</v>
       </c>
-      <c r="L24" s="265">
+      <c r="L24" s="276">
         <v>7.42</v>
       </c>
-      <c r="M24" s="275">
+      <c r="M24" s="265">
         <v>-3.31</v>
       </c>
-      <c r="N24" s="276">
+      <c r="N24" s="266">
         <v>-12.15</v>
       </c>
-      <c r="O24" s="266">
+      <c r="O24" s="268">
         <v>-3.4</v>
       </c>
-      <c r="P24" s="267">
+      <c r="P24" s="272">
         <v>-10.01</v>
       </c>
-      <c r="Q24" s="270">
+      <c r="Q24" s="275">
         <v>-19.03</v>
       </c>
-      <c r="R24" s="268">
+      <c r="R24" s="269">
         <v>-27.17</v>
       </c>
-      <c r="S24" s="269">
+      <c r="S24" s="273">
         <v>-25.92</v>
       </c>
-      <c r="T24" s="272">
-        <v>-26.99</v>
+      <c r="T24" s="270">
+        <v>-29.04</v>
       </c>
     </row>
     <row r="25">
@@ -11118,41 +11230,41 @@
       <c r="H25">
         <v>-1.3</v>
       </c>
-      <c r="I25" s="284">
+      <c r="I25" s="287">
         <v>4.38</v>
       </c>
-      <c r="J25" s="285">
+      <c r="J25" s="279">
         <v>12.4</v>
       </c>
-      <c r="K25" s="282">
+      <c r="K25" s="286">
         <v>12.8</v>
       </c>
       <c r="L25" s="288">
         <v>15.71</v>
       </c>
-      <c r="M25" s="283">
+      <c r="M25" s="277">
         <v>22.51</v>
       </c>
-      <c r="N25" s="286">
+      <c r="N25" s="280">
         <v>10.26</v>
       </c>
-      <c r="O25" s="277">
+      <c r="O25" s="281">
         <v>-0.55</v>
       </c>
-      <c r="P25" s="278">
+      <c r="P25" s="282">
         <v>-7.99</v>
       </c>
-      <c r="Q25" s="287">
+      <c r="Q25" s="283">
         <v>-6.89</v>
       </c>
-      <c r="R25" s="279">
+      <c r="R25" s="284">
         <v>-11.49</v>
       </c>
-      <c r="S25" s="280">
+      <c r="S25" s="285">
         <v>-17.58</v>
       </c>
-      <c r="T25" s="281">
-        <v>-22.39</v>
+      <c r="T25" s="278">
+        <v>-28.02</v>
       </c>
     </row>
     <row r="26">
@@ -11181,41 +11293,41 @@
       <c r="H26">
         <v>-2.57</v>
       </c>
-      <c r="I26" s="289">
+      <c r="I26" s="297">
         <v>10.44</v>
       </c>
-      <c r="J26" s="297">
+      <c r="J26" s="298">
         <v>3.45</v>
       </c>
-      <c r="K26" s="290">
+      <c r="K26" s="293">
         <v>5.27</v>
       </c>
-      <c r="L26" s="294">
+      <c r="L26" s="290">
         <v>9.45</v>
       </c>
-      <c r="M26" s="292">
+      <c r="M26" s="294">
         <v>20.4</v>
       </c>
-      <c r="N26" s="295">
+      <c r="N26" s="299">
         <v>25.42</v>
       </c>
-      <c r="O26" s="291">
+      <c r="O26" s="289">
         <v>22.51</v>
       </c>
-      <c r="P26" s="298">
+      <c r="P26" s="295">
         <v>10.26</v>
       </c>
-      <c r="Q26" s="299">
+      <c r="Q26" s="300">
         <v>5.17</v>
       </c>
-      <c r="R26" s="300">
+      <c r="R26" s="291">
         <v>8.26</v>
       </c>
-      <c r="S26" s="296">
+      <c r="S26" s="292">
         <v>1.19</v>
       </c>
-      <c r="T26" s="293">
-        <v>2.69</v>
+      <c r="T26" s="296">
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
@@ -11246,38 +11358,38 @@
       <c r="I27" s="301">
         <v>11.23</v>
       </c>
-      <c r="J27" s="308">
+      <c r="J27" s="307">
         <v>9.47</v>
       </c>
-      <c r="K27" s="309">
+      <c r="K27" s="302">
         <v>17.89</v>
       </c>
-      <c r="L27" s="310">
+      <c r="L27" s="308">
         <v>15.65</v>
       </c>
       <c r="M27" s="304">
         <v>27.16</v>
       </c>
-      <c r="N27" s="311">
+      <c r="N27" s="309">
         <v>14.46</v>
       </c>
-      <c r="O27" s="312">
+      <c r="O27" s="311">
         <v>3.02</v>
       </c>
-      <c r="P27" s="307">
+      <c r="P27" s="312">
         <v>-7.3</v>
       </c>
-      <c r="Q27" s="305">
+      <c r="Q27" s="303">
         <v>-16.56</v>
       </c>
-      <c r="R27" s="302">
+      <c r="R27" s="305">
         <v>-21.68</v>
       </c>
       <c r="S27" s="306">
         <v>-18.25</v>
       </c>
-      <c r="T27" s="303">
-        <v>52</v>
+      <c r="T27" s="310">
+        <v>40.49</v>
       </c>
     </row>
     <row r="28">
@@ -11305,41 +11417,41 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28" s="324">
+      <c r="I28" s="314">
         <v>7.84</v>
       </c>
-      <c r="J28" s="316">
+      <c r="J28" s="315">
         <v>10.96</v>
       </c>
-      <c r="K28" s="313">
+      <c r="K28" s="323">
         <v>23.57</v>
       </c>
-      <c r="L28" s="314">
+      <c r="L28" s="320">
         <v>27.94</v>
       </c>
-      <c r="M28" s="319">
+      <c r="M28" s="321">
         <v>35.94</v>
       </c>
-      <c r="N28" s="315">
+      <c r="N28" s="322">
         <v>20.4</v>
       </c>
-      <c r="O28" s="322">
+      <c r="O28" s="324">
         <v>17.96</v>
       </c>
-      <c r="P28" s="323">
+      <c r="P28" s="316">
         <v>37.01</v>
       </c>
       <c r="Q28" s="317">
         <v>21.7</v>
       </c>
-      <c r="R28" s="320">
+      <c r="R28" s="318">
         <v>12.72</v>
       </c>
-      <c r="S28" s="318">
+      <c r="S28" s="313">
         <v>19.21</v>
       </c>
-      <c r="T28" s="321">
-        <v>4.54</v>
+      <c r="T28" s="319">
+        <v>4.82</v>
       </c>
     </row>
     <row r="29">
@@ -11367,41 +11479,41 @@
       <c r="H29">
         <v>-1.84</v>
       </c>
-      <c r="I29" s="326">
+      <c r="I29" s="330">
         <v>3.5</v>
       </c>
-      <c r="J29" s="332">
+      <c r="J29" s="326">
         <v>3.9</v>
       </c>
-      <c r="K29" s="327">
+      <c r="K29" s="336">
         <v>6</v>
       </c>
-      <c r="L29" s="328">
+      <c r="L29" s="331">
         <v>0.91</v>
       </c>
-      <c r="M29" s="329">
+      <c r="M29" s="327">
         <v>2.31</v>
       </c>
-      <c r="N29" s="330">
+      <c r="N29" s="335">
         <v>-2.33</v>
       </c>
-      <c r="O29" s="331">
+      <c r="O29" s="332">
         <v>4.44</v>
       </c>
-      <c r="P29" s="334">
+      <c r="P29" s="328">
         <v>2.76</v>
       </c>
       <c r="Q29" s="333">
         <v>-3.56</v>
       </c>
-      <c r="R29" s="335">
+      <c r="R29" s="329">
         <v>-8.22</v>
       </c>
-      <c r="S29" s="336">
+      <c r="S29" s="334">
         <v>-10.22</v>
       </c>
       <c r="T29" s="325">
-        <v>-2.62</v>
+        <v>-6.55</v>
       </c>
     </row>
     <row r="30">
@@ -11429,13 +11541,13 @@
       <c r="H30">
         <v>0.97</v>
       </c>
-      <c r="I30" s="344">
+      <c r="I30" s="348">
         <v>5.31</v>
       </c>
       <c r="J30" s="342">
         <v>8.18</v>
       </c>
-      <c r="K30" s="348">
+      <c r="K30" s="339">
         <v>-1.59</v>
       </c>
       <c r="L30" s="345">
@@ -11444,26 +11556,26 @@
       <c r="M30" s="337">
         <v>-10.1</v>
       </c>
-      <c r="N30" s="338">
+      <c r="N30" s="343">
         <v>-7.76</v>
       </c>
-      <c r="O30" s="339">
+      <c r="O30" s="344">
         <v>-11.26</v>
       </c>
       <c r="P30" s="340">
         <v>-12.33</v>
       </c>
-      <c r="Q30" s="343">
+      <c r="Q30" s="338">
         <v>-3.51</v>
       </c>
-      <c r="R30" s="346">
+      <c r="R30" s="341">
         <v>-4.78</v>
       </c>
-      <c r="S30" s="341">
+      <c r="S30" s="346">
         <v>-3.08</v>
       </c>
       <c r="T30" s="347">
-        <v>-27.74</v>
+        <v>-30.07</v>
       </c>
     </row>
     <row r="31">
@@ -11491,41 +11603,41 @@
       <c r="H31">
         <v>1.37</v>
       </c>
-      <c r="I31" s="354">
+      <c r="I31" s="349">
         <v>5.49</v>
       </c>
-      <c r="J31" s="356">
+      <c r="J31" s="352">
         <v>16.03</v>
       </c>
       <c r="K31" s="357">
         <v>11.44</v>
       </c>
-      <c r="L31" s="350">
+      <c r="L31" s="353">
         <v>16.78</v>
       </c>
-      <c r="M31" s="355">
+      <c r="M31" s="356">
         <v>5.34</v>
       </c>
-      <c r="N31" s="351">
+      <c r="N31" s="354">
         <v>3.91</v>
       </c>
-      <c r="O31" s="359">
+      <c r="O31" s="350">
         <v>5.27</v>
       </c>
-      <c r="P31" s="360">
+      <c r="P31" s="355">
         <v>-1.96</v>
       </c>
       <c r="Q31" s="358">
         <v>0.53</v>
       </c>
-      <c r="R31" s="352">
+      <c r="R31" s="359">
         <v>-5.49</v>
       </c>
-      <c r="S31" s="349">
+      <c r="S31" s="351">
         <v>-7.37</v>
       </c>
-      <c r="T31" s="353">
-        <v>-14</v>
+      <c r="T31" s="360">
+        <v>-19.94</v>
       </c>
     </row>
     <row r="32">
@@ -11553,41 +11665,41 @@
       <c r="H32">
         <v>0.91</v>
       </c>
-      <c r="I32" s="369">
+      <c r="I32" s="365">
         <v>1.8</v>
       </c>
-      <c r="J32" s="371">
+      <c r="J32" s="370">
         <v>-7.4</v>
       </c>
-      <c r="K32" s="372">
+      <c r="K32" s="371">
         <v>-11.8</v>
       </c>
-      <c r="L32" s="361">
+      <c r="L32" s="372">
         <v>-15.4</v>
       </c>
-      <c r="M32" s="366">
+      <c r="M32" s="368">
         <v>-13.2</v>
       </c>
-      <c r="N32" s="362">
+      <c r="N32" s="361">
         <v>-16.5</v>
       </c>
-      <c r="O32" s="363">
+      <c r="O32" s="366">
         <v>-17.5</v>
       </c>
-      <c r="P32" s="364">
+      <c r="P32" s="362">
         <v>-9.2</v>
       </c>
-      <c r="Q32" s="367">
+      <c r="Q32" s="369">
         <v>-10.4</v>
       </c>
-      <c r="R32" s="370">
+      <c r="R32" s="367">
         <v>-8.8</v>
       </c>
-      <c r="S32" s="368">
+      <c r="S32" s="363">
         <v>-6.6</v>
       </c>
-      <c r="T32" s="365">
-        <v>-32</v>
+      <c r="T32" s="364">
+        <v>-34.2</v>
       </c>
     </row>
     <row r="33">
@@ -11615,41 +11727,41 @@
       <c r="H33">
         <v>3.37</v>
       </c>
-      <c r="I33" s="382">
+      <c r="I33" s="384">
         <v>-2.9</v>
       </c>
-      <c r="J33" s="383">
+      <c r="J33" s="377">
         <v>-4.39</v>
       </c>
       <c r="K33" s="380">
         <v>-9.32</v>
       </c>
-      <c r="L33" s="376">
+      <c r="L33" s="373">
         <v>-9.35</v>
       </c>
-      <c r="M33" s="381">
+      <c r="M33" s="375">
         <v>-14.85</v>
       </c>
-      <c r="N33" s="384">
+      <c r="N33" s="381">
         <v>-16.34</v>
       </c>
-      <c r="O33" s="377">
+      <c r="O33" s="378">
         <v>-15.09</v>
       </c>
-      <c r="P33" s="374">
+      <c r="P33" s="382">
         <v>-16.04</v>
       </c>
-      <c r="Q33" s="378">
+      <c r="Q33" s="383">
         <v>-17.6</v>
       </c>
       <c r="R33" s="379">
         <v>-9.35</v>
       </c>
-      <c r="S33" s="373">
+      <c r="S33" s="374">
         <v>-8.16</v>
       </c>
-      <c r="T33" s="375">
-        <v>-24.29</v>
+      <c r="T33" s="376">
+        <v>-29.79</v>
       </c>
     </row>
     <row r="34">
@@ -11677,41 +11789,41 @@
       <c r="H34">
         <v>1.81</v>
       </c>
-      <c r="I34" s="388">
+      <c r="I34" s="387">
         <v>8.09</v>
       </c>
-      <c r="J34" s="391">
+      <c r="J34" s="395">
         <v>5.96</v>
       </c>
-      <c r="K34" s="389">
+      <c r="K34" s="396">
         <v>4.82</v>
       </c>
-      <c r="L34" s="395">
+      <c r="L34" s="394">
         <v>-0.57</v>
       </c>
-      <c r="M34" s="390">
+      <c r="M34" s="388">
         <v>-6.03</v>
       </c>
-      <c r="N34" s="396">
+      <c r="N34" s="389">
         <v>-8.37</v>
       </c>
-      <c r="O34" s="385">
+      <c r="O34" s="393">
         <v>-4.75</v>
       </c>
-      <c r="P34" s="392">
+      <c r="P34" s="390">
         <v>2.41</v>
       </c>
-      <c r="Q34" s="386">
+      <c r="Q34" s="385">
         <v>1.28</v>
       </c>
-      <c r="R34" s="393">
+      <c r="R34" s="391">
         <v>-0.07</v>
       </c>
-      <c r="S34" s="387">
+      <c r="S34" s="386">
         <v>-2.55</v>
       </c>
-      <c r="T34" s="394">
-        <v>53.62</v>
+      <c r="T34" s="392">
+        <v>41.99</v>
       </c>
     </row>
     <row r="35">
@@ -11739,41 +11851,41 @@
       <c r="H35">
         <v>-3</v>
       </c>
-      <c r="I35" s="408">
+      <c r="I35" s="407">
         <v>-7.21</v>
       </c>
-      <c r="J35" s="403">
+      <c r="J35" s="401">
         <v>-5.8</v>
       </c>
       <c r="K35" s="404">
         <v>-7.63</v>
       </c>
-      <c r="L35" s="397">
+      <c r="L35" s="405">
         <v>-15.49</v>
       </c>
-      <c r="M35" s="405">
+      <c r="M35" s="408">
         <v>-23.94</v>
       </c>
-      <c r="N35" s="406">
+      <c r="N35" s="398">
         <v>-20.49</v>
       </c>
-      <c r="O35" s="398">
+      <c r="O35" s="399">
         <v>-25.23</v>
       </c>
-      <c r="P35" s="399">
+      <c r="P35" s="402">
         <v>-22.56</v>
       </c>
-      <c r="Q35" s="400">
+      <c r="Q35" s="403">
         <v>-25.72</v>
       </c>
-      <c r="R35" s="401">
+      <c r="R35" s="406">
         <v>-26.94</v>
       </c>
-      <c r="S35" s="407">
+      <c r="S35" s="397">
         <v>-26.81</v>
       </c>
-      <c r="T35" s="402">
-        <v>-44.84</v>
+      <c r="T35" s="400">
+        <v>-48.23</v>
       </c>
     </row>
     <row r="36">
@@ -11801,41 +11913,41 @@
       <c r="H36">
         <v>5.94</v>
       </c>
-      <c r="I36" s="413">
+      <c r="I36" s="416">
         <v>3.84</v>
       </c>
-      <c r="J36" s="414">
+      <c r="J36" s="413">
         <v>-6.54</v>
       </c>
-      <c r="K36" s="410">
+      <c r="K36" s="417">
         <v>-15.9</v>
       </c>
       <c r="L36" s="411">
         <v>-16.95</v>
       </c>
-      <c r="M36" s="415">
+      <c r="M36" s="409">
         <v>-17.11</v>
       </c>
       <c r="N36" s="418">
         <v>-23.13</v>
       </c>
-      <c r="O36" s="419">
+      <c r="O36" s="410">
         <v>-26.61</v>
       </c>
-      <c r="P36" s="420">
+      <c r="P36" s="419">
         <v>-26.41</v>
       </c>
-      <c r="Q36" s="416">
+      <c r="Q36" s="420">
         <v>-24.65</v>
       </c>
-      <c r="R36" s="417">
+      <c r="R36" s="412">
         <v>-24.54</v>
       </c>
-      <c r="S36" s="412">
+      <c r="S36" s="414">
         <v>-24.32</v>
       </c>
-      <c r="T36" s="409">
-        <v>-27.77</v>
+      <c r="T36" s="415">
+        <v>-30.64</v>
       </c>
     </row>
     <row r="37">
@@ -11863,41 +11975,41 @@
       <c r="H37">
         <v>1.86</v>
       </c>
-      <c r="I37" s="427">
+      <c r="I37" s="429">
         <v>-7.6</v>
       </c>
-      <c r="J37" s="428">
+      <c r="J37" s="423">
         <v>-2.8</v>
       </c>
-      <c r="K37" s="429">
+      <c r="K37" s="424">
         <v>6.09</v>
       </c>
-      <c r="L37" s="430">
+      <c r="L37" s="426">
         <v>10.62</v>
       </c>
-      <c r="M37" s="431">
+      <c r="M37" s="430">
         <v>4.62</v>
       </c>
-      <c r="N37" s="423">
+      <c r="N37" s="427">
         <v>15.1</v>
       </c>
-      <c r="O37" s="432">
+      <c r="O37" s="425">
         <v>12.08</v>
       </c>
-      <c r="P37" s="424">
+      <c r="P37" s="431">
         <v>6.89</v>
       </c>
-      <c r="Q37" s="421">
+      <c r="Q37" s="432">
         <v>17.59</v>
       </c>
-      <c r="R37" s="425">
+      <c r="R37" s="421">
         <v>24.57</v>
       </c>
-      <c r="S37" s="426">
+      <c r="S37" s="428">
         <v>28.83</v>
       </c>
       <c r="T37" s="422">
-        <v>-3.64</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="38">
@@ -11925,41 +12037,41 @@
       <c r="H38">
         <v>-1.77</v>
       </c>
-      <c r="I38" s="443">
+      <c r="I38" s="442">
         <v>-4.39</v>
       </c>
-      <c r="J38" s="444">
+      <c r="J38" s="434">
         <v>2.66</v>
       </c>
-      <c r="K38" s="441">
+      <c r="K38" s="436">
         <v>3.96</v>
       </c>
-      <c r="L38" s="435">
+      <c r="L38" s="443">
         <v>14.33</v>
       </c>
-      <c r="M38" s="439">
+      <c r="M38" s="437">
         <v>14.83</v>
       </c>
-      <c r="N38" s="442">
+      <c r="N38" s="438">
         <v>13.82</v>
       </c>
-      <c r="O38" s="436">
+      <c r="O38" s="440">
         <v>19.44</v>
       </c>
-      <c r="P38" s="433">
+      <c r="P38" s="444">
         <v>23.54</v>
       </c>
-      <c r="Q38" s="440">
+      <c r="Q38" s="439">
         <v>11.16</v>
       </c>
-      <c r="R38" s="437">
+      <c r="R38" s="433">
         <v>0.07</v>
       </c>
-      <c r="S38" s="438">
+      <c r="S38" s="441">
         <v>0.07</v>
       </c>
-      <c r="T38" s="434">
-        <v>18</v>
+      <c r="T38" s="435">
+        <v>13.25</v>
       </c>
     </row>
     <row r="39">
@@ -11987,41 +12099,41 @@
       <c r="H39">
         <v>0.25</v>
       </c>
-      <c r="I39" s="445">
+      <c r="I39" s="448">
         <v>1.06</v>
       </c>
       <c r="J39" s="453">
         <v>-0.81</v>
       </c>
-      <c r="K39" s="446">
+      <c r="K39" s="454">
         <v>-2.94</v>
       </c>
-      <c r="L39" s="450">
+      <c r="L39" s="446">
         <v>-1.31</v>
       </c>
-      <c r="M39" s="451">
+      <c r="M39" s="449">
         <v>-2.56</v>
       </c>
-      <c r="N39" s="447">
+      <c r="N39" s="455">
         <v>0.44</v>
       </c>
-      <c r="O39" s="454">
+      <c r="O39" s="456">
         <v>-3.44</v>
       </c>
-      <c r="P39" s="455">
+      <c r="P39" s="445">
         <v>-13.12</v>
       </c>
-      <c r="Q39" s="448">
+      <c r="Q39" s="451">
         <v>-21.8</v>
       </c>
-      <c r="R39" s="456">
+      <c r="R39" s="447">
         <v>-19.43</v>
       </c>
-      <c r="S39" s="449">
+      <c r="S39" s="450">
         <v>-18.68</v>
       </c>
       <c r="T39" s="452">
-        <v>-21.24</v>
+        <v>-20.11</v>
       </c>
     </row>
     <row r="40">
@@ -12052,38 +12164,38 @@
       <c r="I40" s="466">
         <v>-2.69</v>
       </c>
-      <c r="J40" s="460">
+      <c r="J40" s="457">
         <v>-9.6</v>
       </c>
-      <c r="K40" s="467">
+      <c r="K40" s="459">
         <v>-8.57</v>
       </c>
-      <c r="L40" s="468">
+      <c r="L40" s="467">
         <v>-8.94</v>
       </c>
-      <c r="M40" s="457">
+      <c r="M40" s="460">
         <v>-4.65</v>
       </c>
-      <c r="N40" s="458">
+      <c r="N40" s="464">
         <v>-6.59</v>
       </c>
-      <c r="O40" s="462">
+      <c r="O40" s="458">
         <v>-12.86</v>
       </c>
-      <c r="P40" s="461">
+      <c r="P40" s="468">
         <v>-16.02</v>
       </c>
-      <c r="Q40" s="463">
+      <c r="Q40" s="461">
         <v>-14.33</v>
       </c>
-      <c r="R40" s="464">
+      <c r="R40" s="465">
         <v>-12.49</v>
       </c>
-      <c r="S40" s="459">
+      <c r="S40" s="462">
         <v>-17.56</v>
       </c>
-      <c r="T40" s="465">
-        <v>-6.17</v>
+      <c r="T40" s="463">
+        <v>-14.18</v>
       </c>
     </row>
     <row r="41">
@@ -12111,41 +12223,41 @@
       <c r="H41">
         <v>0.15</v>
       </c>
-      <c r="I41" s="480">
+      <c r="I41" s="475">
         <v>-6.07</v>
       </c>
-      <c r="J41" s="474">
+      <c r="J41" s="470">
         <v>-15.32</v>
       </c>
-      <c r="K41" s="475">
+      <c r="K41" s="472">
         <v>-17.44</v>
       </c>
-      <c r="L41" s="469">
+      <c r="L41" s="473">
         <v>-13.75</v>
       </c>
-      <c r="M41" s="470">
+      <c r="M41" s="479">
         <v>-12.79</v>
       </c>
       <c r="N41" s="476">
         <v>-21.49</v>
       </c>
-      <c r="O41" s="479">
+      <c r="O41" s="471">
         <v>-22.75</v>
       </c>
-      <c r="P41" s="477">
+      <c r="P41" s="480">
         <v>-24.62</v>
       </c>
-      <c r="Q41" s="478">
+      <c r="Q41" s="477">
         <v>-28.06</v>
       </c>
-      <c r="R41" s="471">
+      <c r="R41" s="478">
         <v>-25.68</v>
       </c>
-      <c r="S41" s="472">
+      <c r="S41" s="474">
         <v>-28.61</v>
       </c>
-      <c r="T41" s="473">
-        <v>-34.28</v>
+      <c r="T41" s="469">
+        <v>-33.97</v>
       </c>
     </row>
     <row r="42">
@@ -12173,41 +12285,41 @@
       <c r="H42">
         <v>-7.05</v>
       </c>
-      <c r="I42" s="487">
+      <c r="I42" s="492">
         <v>11.04</v>
       </c>
-      <c r="J42" s="484">
+      <c r="J42" s="485">
         <v>0</v>
       </c>
-      <c r="K42" s="492">
+      <c r="K42" s="488">
         <v>-2.39</v>
       </c>
-      <c r="L42" s="485">
+      <c r="L42" s="481">
         <v>-5.85</v>
       </c>
-      <c r="M42" s="481">
+      <c r="M42" s="486">
         <v>0</v>
       </c>
-      <c r="N42" s="488">
+      <c r="N42" s="487">
         <v>2.13</v>
       </c>
-      <c r="O42" s="489">
+      <c r="O42" s="491">
         <v>-5.05</v>
       </c>
-      <c r="P42" s="490">
+      <c r="P42" s="482">
         <v>-11.7</v>
       </c>
-      <c r="Q42" s="482">
+      <c r="Q42" s="483">
         <v>-2.93</v>
       </c>
-      <c r="R42" s="491">
+      <c r="R42" s="484">
         <v>6.78</v>
       </c>
-      <c r="S42" s="486">
+      <c r="S42" s="489">
         <v>7.05</v>
       </c>
-      <c r="T42" s="483">
-        <v>34.57</v>
+      <c r="T42" s="490">
+        <v>43.62</v>
       </c>
     </row>
     <row r="43">
@@ -12235,41 +12347,41 @@
       <c r="H43">
         <v>3.03</v>
       </c>
-      <c r="I43" s="499">
+      <c r="I43" s="493">
         <v>0</v>
       </c>
-      <c r="J43" s="494">
+      <c r="J43" s="496">
         <v>1.71</v>
       </c>
-      <c r="K43" s="495">
+      <c r="K43" s="494">
         <v>-7.41</v>
       </c>
-      <c r="L43" s="503">
+      <c r="L43" s="497">
         <v>-10.29</v>
       </c>
-      <c r="M43" s="493">
+      <c r="M43" s="498">
         <v>-1.29</v>
       </c>
-      <c r="N43" s="500">
+      <c r="N43" s="495">
         <v>-3.47</v>
       </c>
-      <c r="O43" s="496">
+      <c r="O43" s="499">
         <v>-3</v>
       </c>
-      <c r="P43" s="497">
+      <c r="P43" s="501">
         <v>-1.76</v>
       </c>
-      <c r="Q43" s="501">
+      <c r="Q43" s="502">
         <v>-0.88</v>
       </c>
-      <c r="R43" s="498">
+      <c r="R43" s="503">
         <v>9.06</v>
       </c>
-      <c r="S43" s="502">
+      <c r="S43" s="500">
         <v>13.29</v>
       </c>
       <c r="T43" s="504">
-        <v>27.41</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="44">
@@ -12297,41 +12409,41 @@
       <c r="H44">
         <v>-0.8</v>
       </c>
-      <c r="I44" s="514">
+      <c r="I44" s="513">
         <v>-1.61</v>
       </c>
       <c r="J44" s="515">
         <v>-5.09</v>
       </c>
-      <c r="K44" s="509">
+      <c r="K44" s="507">
         <v>0.8</v>
       </c>
-      <c r="L44" s="510">
+      <c r="L44" s="508">
         <v>2.95</v>
       </c>
-      <c r="M44" s="511">
+      <c r="M44" s="505">
         <v>-4.29</v>
       </c>
-      <c r="N44" s="505">
+      <c r="N44" s="509">
         <v>-10.99</v>
       </c>
-      <c r="O44" s="506">
+      <c r="O44" s="510">
         <v>-2.14</v>
       </c>
-      <c r="P44" s="513">
+      <c r="P44" s="516">
         <v>7.64</v>
       </c>
-      <c r="Q44" s="512">
+      <c r="Q44" s="511">
         <v>7.91</v>
       </c>
-      <c r="R44" s="507">
+      <c r="R44" s="514">
         <v>-2.28</v>
       </c>
-      <c r="S44" s="508">
+      <c r="S44" s="506">
         <v>-4.29</v>
       </c>
-      <c r="T44" s="516">
-        <v>35.66</v>
+      <c r="T44" s="512">
+        <v>44.77</v>
       </c>
     </row>
     <row r="45">
@@ -12359,39 +12471,41 @@
       <c r="H45">
         <v>3.19</v>
       </c>
-      <c r="I45" s="522">
+      <c r="I45" s="521">
         <v>1.28</v>
       </c>
       <c r="J45" s="527">
         <v>11.43</v>
       </c>
-      <c r="K45" s="523">
+      <c r="K45" s="524">
         <v>14.73</v>
       </c>
-      <c r="L45" s="517">
+      <c r="L45" s="522">
         <v>14.86</v>
       </c>
-      <c r="M45" s="524">
+      <c r="M45" s="525">
         <v>26.36</v>
       </c>
-      <c r="N45" s="518">
+      <c r="N45" s="528">
         <v>15</v>
       </c>
-      <c r="O45" s="519">
+      <c r="O45" s="526">
         <v>17.69</v>
       </c>
-      <c r="P45" s="520">
+      <c r="P45" s="517">
         <v>20.85</v>
       </c>
-      <c r="Q45" s="525">
+      <c r="Q45" s="518">
         <v>12.64</v>
       </c>
-      <c r="R45" s="526">
+      <c r="R45" s="519">
         <v>10.22</v>
       </c>
-      <c r="S45" t="str"/>
-      <c r="T45" s="521">
-        <v>10.22</v>
+      <c r="S45" s="523">
+        <v>5.78</v>
+      </c>
+      <c r="T45" s="520">
+        <v>5.78</v>
       </c>
     </row>
     <row r="46">
@@ -12419,37 +12533,39 @@
       <c r="H46">
         <v>6.57</v>
       </c>
-      <c r="I46" s="529">
+      <c r="I46" s="531">
         <v>3.23</v>
       </c>
-      <c r="J46" s="535">
+      <c r="J46" s="533">
         <v>13.56</v>
       </c>
       <c r="K46" s="532">
         <v>24.92</v>
       </c>
-      <c r="L46" s="537">
+      <c r="L46" s="534">
         <v>34.8</v>
       </c>
-      <c r="M46" s="528">
+      <c r="M46" s="535">
         <v>21.32</v>
       </c>
-      <c r="N46" s="530">
+      <c r="N46" s="539">
         <v>9.19</v>
       </c>
-      <c r="O46" s="533">
+      <c r="O46" s="529">
         <v>10.17</v>
       </c>
-      <c r="P46" s="531">
+      <c r="P46" s="530">
         <v>13.15</v>
       </c>
       <c r="Q46" s="536">
         <v>17.73</v>
       </c>
-      <c r="R46" t="str"/>
+      <c r="R46" s="537">
+        <v>20.51</v>
+      </c>
       <c r="S46" t="str"/>
-      <c r="T46" s="534">
-        <v>17.73</v>
+      <c r="T46" s="538">
+        <v>20.51</v>
       </c>
     </row>
     <row r="47">
@@ -12477,29 +12593,31 @@
       <c r="H47">
         <v>-3.47</v>
       </c>
-      <c r="I47" s="540">
+      <c r="I47" s="541">
         <v>11.54</v>
       </c>
-      <c r="J47" s="541">
+      <c r="J47" s="542">
         <v>16.51</v>
       </c>
-      <c r="K47" s="542">
+      <c r="K47" s="543">
         <v>28.13</v>
       </c>
-      <c r="L47" s="543">
+      <c r="L47" s="544">
         <v>24.16</v>
       </c>
-      <c r="M47" s="538">
+      <c r="M47" s="545">
         <v>26.22</v>
       </c>
-      <c r="N47" t="str"/>
+      <c r="N47" s="546">
+        <v>21.56</v>
+      </c>
       <c r="O47" t="str"/>
       <c r="P47" t="str"/>
       <c r="Q47" t="str"/>
       <c r="R47" t="str"/>
       <c r="S47" t="str"/>
-      <c r="T47" s="539">
-        <v>26.22</v>
+      <c r="T47" s="540">
+        <v>21.56</v>
       </c>
     </row>
     <row r="48">
@@ -12527,29 +12645,31 @@
       <c r="H48">
         <v>-0.07</v>
       </c>
-      <c r="I48" s="548">
+      <c r="I48" s="547">
         <v>1.12</v>
       </c>
-      <c r="J48" s="549">
+      <c r="J48" s="548">
         <v>0.16</v>
       </c>
-      <c r="K48" s="544">
+      <c r="K48" s="549">
         <v>-0.32</v>
       </c>
-      <c r="L48" s="545">
+      <c r="L48" s="550">
         <v>-4.53</v>
       </c>
-      <c r="M48" s="546">
+      <c r="M48" s="551">
         <v>-5.77</v>
       </c>
-      <c r="N48" t="str"/>
+      <c r="N48" s="552">
+        <v>-8.4</v>
+      </c>
       <c r="O48" t="str"/>
       <c r="P48" t="str"/>
       <c r="Q48" t="str"/>
       <c r="R48" t="str"/>
       <c r="S48" t="str"/>
-      <c r="T48" s="547">
-        <v>-5.77</v>
+      <c r="T48" s="553">
+        <v>-8.4</v>
       </c>
     </row>
     <row r="49">
@@ -12577,29 +12697,31 @@
       <c r="H49">
         <v>-0.16</v>
       </c>
-      <c r="I49" s="554">
+      <c r="I49" s="558">
         <v>-1.41</v>
       </c>
-      <c r="J49" s="555">
+      <c r="J49" s="559">
         <v>2.5</v>
       </c>
-      <c r="K49" s="550">
+      <c r="K49" s="560">
         <v>5.31</v>
       </c>
-      <c r="L49" s="551">
+      <c r="L49" s="554">
         <v>-4.38</v>
       </c>
-      <c r="M49" s="552">
+      <c r="M49" s="555">
         <v>-12.19</v>
       </c>
-      <c r="N49" t="str"/>
+      <c r="N49" s="556">
+        <v>-3.44</v>
+      </c>
       <c r="O49" t="str"/>
       <c r="P49" t="str"/>
       <c r="Q49" t="str"/>
       <c r="R49" t="str"/>
       <c r="S49" t="str"/>
-      <c r="T49" s="553">
-        <v>-12.19</v>
+      <c r="T49" s="557">
+        <v>-3.44</v>
       </c>
     </row>
     <row r="50">
@@ -12627,10 +12749,12 @@
       <c r="H50">
         <v>-1.59</v>
       </c>
-      <c r="I50" s="556">
+      <c r="I50" s="562">
         <v>5.72</v>
       </c>
-      <c r="J50" t="str"/>
+      <c r="J50" s="563">
+        <v>8.22</v>
+      </c>
       <c r="K50" t="str"/>
       <c r="L50" t="str"/>
       <c r="M50" t="str"/>
@@ -12640,7 +12764,9 @@
       <c r="Q50" t="str"/>
       <c r="R50" t="str"/>
       <c r="S50" t="str"/>
-      <c r="T50" t="str"/>
+      <c r="T50" s="561">
+        <v>8.22</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -12657,7 +12783,7 @@
         <v>49</v>
       </c>
       <c r="J51">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K51">
         <v>48</v>
@@ -12669,7 +12795,7 @@
         <v>48</v>
       </c>
       <c r="N51">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O51">
         <v>45</v>
@@ -12681,13 +12807,13 @@
         <v>45</v>
       </c>
       <c r="R51">
+        <v>45</v>
+      </c>
+      <c r="S51">
         <v>44</v>
       </c>
-      <c r="S51">
-        <v>43</v>
-      </c>
       <c r="T51">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -12701,41 +12827,41 @@
       <c r="F52" t="str"/>
       <c r="G52" t="str"/>
       <c r="H52" t="str"/>
-      <c r="I52" s="566">
+      <c r="I52" s="570">
         <v>67.35</v>
       </c>
-      <c r="J52" s="560">
-        <v>60.42</v>
-      </c>
-      <c r="K52" s="562">
+      <c r="J52" s="574">
+        <v>61.22</v>
+      </c>
+      <c r="K52" s="571">
         <v>56.25</v>
       </c>
-      <c r="L52" s="564">
+      <c r="L52" s="575">
         <v>54.17</v>
       </c>
-      <c r="M52" s="567">
+      <c r="M52" s="568">
         <v>47.92</v>
       </c>
-      <c r="N52" s="565">
-        <v>53.33</v>
-      </c>
-      <c r="O52" s="568">
+      <c r="N52" s="564">
+        <v>52.08</v>
+      </c>
+      <c r="O52" s="565">
         <v>51.11</v>
       </c>
-      <c r="P52" s="563">
+      <c r="P52" s="569">
         <v>51.11</v>
       </c>
-      <c r="Q52" s="561">
+      <c r="Q52" s="572">
         <v>51.11</v>
       </c>
-      <c r="R52" s="557">
-        <v>50</v>
-      </c>
-      <c r="S52" s="558">
-        <v>41.86</v>
-      </c>
-      <c r="T52" s="559">
-        <v>41.67</v>
+      <c r="R52" s="566">
+        <v>51.11</v>
+      </c>
+      <c r="S52" s="567">
+        <v>43.18</v>
+      </c>
+      <c r="T52" s="573">
+        <v>42.86</v>
       </c>
     </row>
     <row r="53">
@@ -12749,41 +12875,41 @@
       <c r="F53" t="str"/>
       <c r="G53" t="str"/>
       <c r="H53" t="str"/>
-      <c r="I53" s="576">
+      <c r="I53" s="583">
         <v>2.72</v>
       </c>
-      <c r="J53" s="579">
-        <v>3.16</v>
-      </c>
-      <c r="K53" s="570">
+      <c r="J53" s="580">
+        <v>3.27</v>
+      </c>
+      <c r="K53" s="584">
         <v>3.1</v>
       </c>
-      <c r="L53" s="572">
+      <c r="L53" s="586">
         <v>2.29</v>
       </c>
-      <c r="M53" s="571">
+      <c r="M53" s="587">
         <v>2.22</v>
       </c>
-      <c r="N53" s="573">
-        <v>0.76</v>
-      </c>
-      <c r="O53" s="577">
+      <c r="N53" s="581">
+        <v>0.91</v>
+      </c>
+      <c r="O53" s="582">
         <v>0.64</v>
       </c>
-      <c r="P53" s="578">
+      <c r="P53" s="576">
         <v>1.2</v>
       </c>
-      <c r="Q53" s="580">
+      <c r="Q53" s="577">
         <v>0.07</v>
       </c>
-      <c r="R53" s="574">
-        <v>-0.67</v>
-      </c>
-      <c r="S53" s="569">
-        <v>-1.34</v>
-      </c>
-      <c r="T53" s="575">
-        <v>-1.01</v>
+      <c r="R53" s="585">
+        <v>-0.19</v>
+      </c>
+      <c r="S53" s="578">
+        <v>-1.17</v>
+      </c>
+      <c r="T53" s="579">
+        <v>-2.88</v>
       </c>
     </row>
   </sheetData>
